--- a/data/raw/procurement_data.xlsx
+++ b/data/raw/procurement_data.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suppliers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchases" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SupplierMetrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Suppliers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Purchases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SupplierMetrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,24 +27,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,11 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,42 +417,34 @@
   </sheetPr>
   <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>supplier_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product_description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
@@ -500,7 +478,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -532,7 +510,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -564,7 +542,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -596,7 +574,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -628,7 +606,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -660,7 +638,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -692,7 +670,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -724,7 +702,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -756,7 +734,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -788,7 +766,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -820,7 +798,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -852,7 +830,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -884,7 +862,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -916,7 +894,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -948,7 +926,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -980,7 +958,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1012,7 +990,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1022,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1054,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1086,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1118,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1150,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1182,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1214,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1246,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1278,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1310,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1342,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1374,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1406,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1438,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1470,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1502,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1534,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1566,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1598,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1630,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1662,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1694,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1726,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1758,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1790,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1822,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1854,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1886,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1918,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1950,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -2004,7 +1982,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2014,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2046,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2078,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2110,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2142,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2174,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2206,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -2245,138 +2223,114 @@
   </sheetPr>
   <dimension ref="A1:V641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="25" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="19" customWidth="1" min="22" max="22"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>po_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>supplier_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>item_description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>unit_price_usd</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>total_value_usd</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>pr_date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>po_date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>delivery_date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>invoice_date</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>payment_date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>pr_to_po_days</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>po_to_delivery_days</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>delivery_to_invoice_days</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>invoice_to_payment_days</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>total_cycle_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>on_time_delivery</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>three_way_match_pass</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>automation_period</t>
         </is>
@@ -61275,162 +61229,134 @@
   </sheetPr>
   <dimension ref="A1:Z56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="17" customWidth="1" min="24" max="24"/>
-    <col width="17" customWidth="1" min="25" max="25"/>
-    <col width="15" customWidth="1" min="26" max="26"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>supplier_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>product_description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_spend_usd</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>num_pos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_po_value_usd</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_lead_time_days</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_cycle_time_days</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>on_time_delivery_pct</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>three_way_match_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>defect_rate_pct</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>complaint_count_annual</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rfx_response_rate_pct</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>avg_response_time_days</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>single_source_risk</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>quality_score</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>delivery_score</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>service_score</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>process_score</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>risk_score</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>composite_score</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>calculated_tier</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>tier_mismatch</t>
         </is>
@@ -61464,7 +61390,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -61516,14 +61442,14 @@
         <v>84.62</v>
       </c>
       <c r="W2" t="n">
-        <v>100</v>
+        <v>41.31</v>
       </c>
       <c r="X2" t="n">
-        <v>87.15000000000001</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z2" t="b">
@@ -61558,7 +61484,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -61610,18 +61536,18 @@
         <v>78.56999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>100</v>
+        <v>18.74</v>
       </c>
       <c r="X3" t="n">
-        <v>86.23999999999999</v>
+        <v>74.67</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -61652,7 +61578,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -61704,14 +61630,14 @@
         <v>67.73999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>100</v>
+        <v>47.51</v>
       </c>
       <c r="X4" t="n">
-        <v>83.76000000000001</v>
+        <v>76</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z4" t="b">
@@ -61746,7 +61672,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -61798,14 +61724,14 @@
         <v>88.45999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>100</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>80.83</v>
+        <v>77.55</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z5" t="b">
@@ -61840,7 +61766,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -61892,14 +61818,14 @@
         <v>69.23</v>
       </c>
       <c r="W6" t="n">
-        <v>100</v>
+        <v>30.1</v>
       </c>
       <c r="X6" t="n">
-        <v>73.58</v>
+        <v>64.25</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z6" t="b">
@@ -61934,7 +61860,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -61986,18 +61912,18 @@
         <v>73.33</v>
       </c>
       <c r="W7" t="n">
-        <v>100</v>
+        <v>33.6</v>
       </c>
       <c r="X7" t="n">
-        <v>78.19</v>
+        <v>69.02</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -62028,7 +61954,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -62080,14 +62006,14 @@
         <v>100</v>
       </c>
       <c r="W8" t="n">
-        <v>100</v>
+        <v>58.81</v>
       </c>
       <c r="X8" t="n">
-        <v>72.17</v>
+        <v>69.08</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z8" t="b">
@@ -62122,7 +62048,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -62174,14 +62100,14 @@
         <v>91.67</v>
       </c>
       <c r="W9" t="n">
-        <v>100</v>
+        <v>56.26</v>
       </c>
       <c r="X9" t="n">
-        <v>74.76000000000001</v>
+        <v>69.59</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z9" t="b">
@@ -62216,7 +62142,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -62268,18 +62194,18 @@
         <v>63.64</v>
       </c>
       <c r="W10" t="n">
-        <v>100</v>
+        <v>48.16</v>
       </c>
       <c r="X10" t="n">
-        <v>78.18000000000001</v>
+        <v>71.72</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -62310,7 +62236,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -62362,18 +62288,18 @@
         <v>73.91</v>
       </c>
       <c r="W11" t="n">
-        <v>100</v>
+        <v>44.97</v>
       </c>
       <c r="X11" t="n">
-        <v>80.03</v>
+        <v>72.2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -62404,7 +62330,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -62456,14 +62382,14 @@
         <v>75</v>
       </c>
       <c r="W12" t="n">
-        <v>100</v>
+        <v>71.25</v>
       </c>
       <c r="X12" t="n">
-        <v>79.83</v>
+        <v>77.14</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -62498,7 +62424,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -62535,7 +62461,7 @@
         <v>4.37</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>62.48</v>
@@ -62550,14 +62476,14 @@
         <v>77.78</v>
       </c>
       <c r="W13" t="n">
-        <v>100</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>69.29000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z13" t="b">
@@ -62592,7 +62518,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -62644,14 +62570,14 @@
         <v>66.67</v>
       </c>
       <c r="W14" t="n">
-        <v>100</v>
+        <v>56.88</v>
       </c>
       <c r="X14" t="n">
-        <v>71.98999999999999</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z14" t="b">
@@ -62686,7 +62612,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -62723,7 +62649,7 @@
         <v>1.26</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>89.18000000000001</v>
@@ -62738,14 +62664,14 @@
         <v>55.17</v>
       </c>
       <c r="W15" t="n">
-        <v>100</v>
+        <v>67.05</v>
       </c>
       <c r="X15" t="n">
-        <v>83.11</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z15" t="b">
@@ -62780,7 +62706,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -62832,14 +62758,14 @@
         <v>73.33</v>
       </c>
       <c r="W16" t="n">
-        <v>100</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>81.33</v>
+        <v>76.66</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -62874,7 +62800,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -62926,14 +62852,14 @@
         <v>42.86</v>
       </c>
       <c r="W17" t="n">
-        <v>100</v>
+        <v>34.47</v>
       </c>
       <c r="X17" t="n">
-        <v>67.84</v>
+        <v>58.95</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z17" t="b">
@@ -62968,7 +62894,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -63005,7 +62931,7 @@
         <v>0.68</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>81.20999999999999</v>
@@ -63020,14 +62946,14 @@
         <v>87.5</v>
       </c>
       <c r="W18" t="n">
-        <v>100</v>
+        <v>50.48</v>
       </c>
       <c r="X18" t="n">
-        <v>85.73999999999999</v>
+        <v>79.25</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z18" t="b">
@@ -63062,7 +62988,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -63099,7 +63025,7 @@
         <v>2.98</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>74.19</v>
@@ -63114,14 +63040,14 @@
         <v>53.33</v>
       </c>
       <c r="W19" t="n">
-        <v>100</v>
+        <v>32.57</v>
       </c>
       <c r="X19" t="n">
-        <v>72.39</v>
+        <v>63.57</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z19" t="b">
@@ -63156,7 +63082,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -63208,14 +63134,14 @@
         <v>50</v>
       </c>
       <c r="W20" t="n">
-        <v>100</v>
+        <v>71.72</v>
       </c>
       <c r="X20" t="n">
-        <v>71.36</v>
+        <v>68.97</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z20" t="b">
@@ -63250,7 +63176,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -63302,14 +63228,14 @@
         <v>84.62</v>
       </c>
       <c r="W21" t="n">
-        <v>100</v>
+        <v>64.08</v>
       </c>
       <c r="X21" t="n">
-        <v>69.17</v>
+        <v>65.62</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -63344,7 +63270,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -63396,14 +63322,14 @@
         <v>87.5</v>
       </c>
       <c r="W22" t="n">
-        <v>100</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>72.40000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z22" t="b">
@@ -63438,7 +63364,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -63490,14 +63416,14 @@
         <v>50</v>
       </c>
       <c r="W23" t="n">
-        <v>100</v>
+        <v>52.73</v>
       </c>
       <c r="X23" t="n">
-        <v>63.95</v>
+        <v>58.57</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z23" t="b">
@@ -63532,7 +63458,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -63584,14 +63510,14 @@
         <v>77.78</v>
       </c>
       <c r="W24" t="n">
-        <v>100</v>
+        <v>65.06</v>
       </c>
       <c r="X24" t="n">
-        <v>84.73999999999999</v>
+        <v>79.98</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z24" t="b">
@@ -63626,7 +63552,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -63678,14 +63604,14 @@
         <v>96.15000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>100</v>
+        <v>48.76</v>
       </c>
       <c r="X25" t="n">
-        <v>82.62</v>
+        <v>76.22</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z25" t="b">
@@ -63720,7 +63646,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -63772,18 +63698,18 @@
         <v>54.84</v>
       </c>
       <c r="W26" t="n">
-        <v>100</v>
+        <v>37.34</v>
       </c>
       <c r="X26" t="n">
-        <v>80.68000000000001</v>
+        <v>71.64</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -63814,7 +63740,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -63866,18 +63792,18 @@
         <v>100</v>
       </c>
       <c r="W27" t="n">
-        <v>100</v>
+        <v>46.27</v>
       </c>
       <c r="X27" t="n">
-        <v>77.14</v>
+        <v>70.84</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -63908,7 +63834,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -63960,14 +63886,14 @@
         <v>66.67</v>
       </c>
       <c r="W28" t="n">
-        <v>100</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="X28" t="n">
-        <v>72.20999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z28" t="b">
@@ -64002,7 +63928,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -64039,7 +63965,7 @@
         <v>13.76</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>58.39</v>
@@ -64054,14 +63980,14 @@
         <v>100</v>
       </c>
       <c r="W29" t="n">
-        <v>100</v>
+        <v>59.31</v>
       </c>
       <c r="X29" t="n">
-        <v>71.28</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z29" t="b">
@@ -64096,7 +64022,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -64148,18 +64074,18 @@
         <v>100</v>
       </c>
       <c r="W30" t="n">
-        <v>100</v>
+        <v>57.33</v>
       </c>
       <c r="X30" t="n">
-        <v>59.87</v>
+        <v>56.68</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -64190,7 +64116,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -64242,18 +64168,18 @@
         <v>81.81999999999999</v>
       </c>
       <c r="W31" t="n">
-        <v>100</v>
+        <v>63.49</v>
       </c>
       <c r="X31" t="n">
-        <v>79.93000000000001</v>
+        <v>74.77</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -64284,7 +64210,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -64336,14 +64262,14 @@
         <v>77.78</v>
       </c>
       <c r="W32" t="n">
-        <v>100</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="X32" t="n">
-        <v>76.87</v>
+        <v>76.22</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z32" t="b">
@@ -64378,7 +64304,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -64415,7 +64341,7 @@
         <v>2.28</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>53.61</v>
@@ -64430,14 +64356,14 @@
         <v>57.14</v>
       </c>
       <c r="W33" t="n">
-        <v>100</v>
+        <v>56.77</v>
       </c>
       <c r="X33" t="n">
-        <v>64.11</v>
+        <v>59.95</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z33" t="b">
@@ -64472,7 +64398,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -64524,14 +64450,14 @@
         <v>70</v>
       </c>
       <c r="W34" t="n">
-        <v>100</v>
+        <v>61.66</v>
       </c>
       <c r="X34" t="n">
-        <v>56.73</v>
+        <v>54.28</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="Z34" t="b">
@@ -64566,7 +64492,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -64618,14 +64544,14 @@
         <v>87.5</v>
       </c>
       <c r="W35" t="n">
-        <v>100</v>
+        <v>59.27</v>
       </c>
       <c r="X35" t="n">
-        <v>64.48999999999999</v>
+        <v>60.99</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z35" t="b">
@@ -64660,7 +64586,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -64712,18 +64638,18 @@
         <v>50</v>
       </c>
       <c r="W36" t="n">
-        <v>100</v>
+        <v>70.05</v>
       </c>
       <c r="X36" t="n">
-        <v>56.93</v>
+        <v>56.61</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -64754,7 +64680,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -64806,14 +64732,14 @@
         <v>86.67</v>
       </c>
       <c r="W37" t="n">
-        <v>100</v>
+        <v>88.16</v>
       </c>
       <c r="X37" t="n">
-        <v>71.2</v>
+        <v>70.58</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z37" t="b">
@@ -64848,7 +64774,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -64900,14 +64826,14 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>100</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="X38" t="n">
-        <v>47.96</v>
+        <v>46.07</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="Z38" t="b">
@@ -64942,7 +64868,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -64994,18 +64920,18 @@
         <v>85.70999999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>100</v>
+        <v>49.83</v>
       </c>
       <c r="X39" t="n">
-        <v>78</v>
+        <v>71.3</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -65036,7 +64962,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -65088,14 +65014,14 @@
         <v>100</v>
       </c>
       <c r="W40" t="n">
-        <v>100</v>
+        <v>59.14</v>
       </c>
       <c r="X40" t="n">
-        <v>62.54</v>
+        <v>59.19</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z40" t="b">
@@ -65130,7 +65056,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -65182,14 +65108,14 @@
         <v>85.70999999999999</v>
       </c>
       <c r="W41" t="n">
-        <v>100</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="X41" t="n">
-        <v>71.41</v>
+        <v>69.03</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z41" t="b">
@@ -65224,7 +65150,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -65261,7 +65187,7 @@
         <v>1.09</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>69.86</v>
@@ -65276,14 +65202,14 @@
         <v>90.91</v>
       </c>
       <c r="W42" t="n">
-        <v>100</v>
+        <v>78.33</v>
       </c>
       <c r="X42" t="n">
-        <v>73.31</v>
+        <v>71.56</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z42" t="b">
@@ -65318,7 +65244,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -65355,7 +65281,7 @@
         <v>6.23</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>49.12</v>
@@ -65370,14 +65296,14 @@
         <v>100</v>
       </c>
       <c r="W43" t="n">
-        <v>100</v>
+        <v>65.77</v>
       </c>
       <c r="X43" t="n">
-        <v>72.28</v>
+        <v>69.69</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z43" t="b">
@@ -65412,7 +65338,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -65464,18 +65390,18 @@
         <v>80.65000000000001</v>
       </c>
       <c r="W44" t="n">
-        <v>100</v>
+        <v>45.76</v>
       </c>
       <c r="X44" t="n">
-        <v>80.87</v>
+        <v>73.06</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -65506,7 +65432,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -65558,14 +65484,14 @@
         <v>100</v>
       </c>
       <c r="W45" t="n">
-        <v>100</v>
+        <v>65.98</v>
       </c>
       <c r="X45" t="n">
-        <v>81.5</v>
+        <v>77.33</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z45" t="b">
@@ -65600,7 +65526,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -65652,14 +65578,14 @@
         <v>66.67</v>
       </c>
       <c r="W46" t="n">
-        <v>100</v>
+        <v>63.84</v>
       </c>
       <c r="X46" t="n">
-        <v>74.25</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -65694,7 +65620,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -65746,18 +65672,18 @@
         <v>93.33</v>
       </c>
       <c r="W47" t="n">
-        <v>100</v>
+        <v>56.82</v>
       </c>
       <c r="X47" t="n">
-        <v>78.86</v>
+        <v>74.14</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -65788,7 +65714,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -65840,14 +65766,14 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>100</v>
+        <v>68.69</v>
       </c>
       <c r="X48" t="n">
-        <v>52.39</v>
+        <v>49.24</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -65882,7 +65808,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -65934,14 +65860,14 @@
         <v>100</v>
       </c>
       <c r="W49" t="n">
-        <v>100</v>
+        <v>59.99</v>
       </c>
       <c r="X49" t="n">
-        <v>77.31</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z49" t="b">
@@ -65976,7 +65902,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -66028,14 +65954,14 @@
         <v>33.33</v>
       </c>
       <c r="W50" t="n">
-        <v>100</v>
+        <v>71.19</v>
       </c>
       <c r="X50" t="n">
-        <v>54.96</v>
+        <v>54.36</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="Z50" t="b">
@@ -66070,7 +65996,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -66122,14 +66048,14 @@
         <v>83.33</v>
       </c>
       <c r="W51" t="n">
-        <v>100</v>
+        <v>51.16</v>
       </c>
       <c r="X51" t="n">
-        <v>69.48999999999999</v>
+        <v>64.84</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z51" t="b">
@@ -66164,7 +66090,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -66201,7 +66127,7 @@
         <v>0.95</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
         <v>70.06999999999999</v>
@@ -66216,14 +66142,14 @@
         <v>100</v>
       </c>
       <c r="W52" t="n">
-        <v>100</v>
+        <v>58.15</v>
       </c>
       <c r="X52" t="n">
-        <v>82.98999999999999</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -66258,7 +66184,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -66295,7 +66221,7 @@
         <v>2.23</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
         <v>22.41</v>
@@ -66310,14 +66236,14 @@
         <v>100</v>
       </c>
       <c r="W53" t="n">
-        <v>100</v>
+        <v>67.3</v>
       </c>
       <c r="X53" t="n">
-        <v>60.2</v>
+        <v>59.17</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -66352,7 +66278,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -66404,14 +66330,14 @@
         <v>100</v>
       </c>
       <c r="W54" t="n">
-        <v>100</v>
+        <v>26.75</v>
       </c>
       <c r="X54" t="n">
-        <v>84.02</v>
+        <v>74.8</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z54" t="b">
@@ -66446,7 +66372,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -66498,14 +66424,14 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>100</v>
+        <v>44.21</v>
       </c>
       <c r="X55" t="n">
-        <v>58.57</v>
+        <v>52.19</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="Z55" t="b">
@@ -66540,7 +66466,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -66577,7 +66503,7 @@
         <v>3.54</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
         <v>42.08</v>
@@ -66592,14 +66518,14 @@
         <v>100</v>
       </c>
       <c r="W56" t="n">
-        <v>100</v>
+        <v>50.49</v>
       </c>
       <c r="X56" t="n">
-        <v>66.48</v>
+        <v>61.95</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Preferred</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z56" t="b">

--- a/data/raw/procurement_data.xlsx
+++ b/data/raw/procurement_data.xlsx
@@ -2221,7 +2221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V641"/>
+  <dimension ref="A1:U641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2330,11 +2330,6 @@
           <t>three_way_match_pass</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>automation_period</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2422,11 +2417,6 @@
       <c r="U2" t="b">
         <v>1</v>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2514,11 +2504,6 @@
       <c r="U3" t="b">
         <v>0</v>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2606,11 +2591,6 @@
       <c r="U4" t="b">
         <v>1</v>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2698,11 +2678,6 @@
       <c r="U5" t="b">
         <v>0</v>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2790,11 +2765,6 @@
       <c r="U6" t="b">
         <v>1</v>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2882,11 +2852,6 @@
       <c r="U7" t="b">
         <v>0</v>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2974,11 +2939,6 @@
       <c r="U8" t="b">
         <v>1</v>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3066,11 +3026,6 @@
       <c r="U9" t="b">
         <v>1</v>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3158,11 +3113,6 @@
       <c r="U10" t="b">
         <v>1</v>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3250,11 +3200,6 @@
       <c r="U11" t="b">
         <v>1</v>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3342,11 +3287,6 @@
       <c r="U12" t="b">
         <v>1</v>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3434,11 +3374,6 @@
       <c r="U13" t="b">
         <v>1</v>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3526,11 +3461,6 @@
       <c r="U14" t="b">
         <v>1</v>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3618,11 +3548,6 @@
       <c r="U15" t="b">
         <v>1</v>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3710,11 +3635,6 @@
       <c r="U16" t="b">
         <v>1</v>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3802,11 +3722,6 @@
       <c r="U17" t="b">
         <v>0</v>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3894,11 +3809,6 @@
       <c r="U18" t="b">
         <v>1</v>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3986,11 +3896,6 @@
       <c r="U19" t="b">
         <v>1</v>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4078,11 +3983,6 @@
       <c r="U20" t="b">
         <v>1</v>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4170,11 +4070,6 @@
       <c r="U21" t="b">
         <v>0</v>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4262,11 +4157,6 @@
       <c r="U22" t="b">
         <v>1</v>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4354,11 +4244,6 @@
       <c r="U23" t="b">
         <v>1</v>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4446,11 +4331,6 @@
       <c r="U24" t="b">
         <v>1</v>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4538,11 +4418,6 @@
       <c r="U25" t="b">
         <v>1</v>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4630,11 +4505,6 @@
       <c r="U26" t="b">
         <v>1</v>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4722,11 +4592,6 @@
       <c r="U27" t="b">
         <v>1</v>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4814,11 +4679,6 @@
       <c r="U28" t="b">
         <v>1</v>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4906,11 +4766,6 @@
       <c r="U29" t="b">
         <v>1</v>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4998,11 +4853,6 @@
       <c r="U30" t="b">
         <v>1</v>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5090,11 +4940,6 @@
       <c r="U31" t="b">
         <v>1</v>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5182,11 +5027,6 @@
       <c r="U32" t="b">
         <v>1</v>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5274,11 +5114,6 @@
       <c r="U33" t="b">
         <v>1</v>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5366,11 +5201,6 @@
       <c r="U34" t="b">
         <v>1</v>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5458,11 +5288,6 @@
       <c r="U35" t="b">
         <v>1</v>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5550,11 +5375,6 @@
       <c r="U36" t="b">
         <v>0</v>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5642,11 +5462,6 @@
       <c r="U37" t="b">
         <v>1</v>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5734,11 +5549,6 @@
       <c r="U38" t="b">
         <v>1</v>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5826,11 +5636,6 @@
       <c r="U39" t="b">
         <v>1</v>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5918,11 +5723,6 @@
       <c r="U40" t="b">
         <v>1</v>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6010,11 +5810,6 @@
       <c r="U41" t="b">
         <v>0</v>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6102,11 +5897,6 @@
       <c r="U42" t="b">
         <v>0</v>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6194,11 +5984,6 @@
       <c r="U43" t="b">
         <v>1</v>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6286,11 +6071,6 @@
       <c r="U44" t="b">
         <v>1</v>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6378,11 +6158,6 @@
       <c r="U45" t="b">
         <v>1</v>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6470,11 +6245,6 @@
       <c r="U46" t="b">
         <v>1</v>
       </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6562,11 +6332,6 @@
       <c r="U47" t="b">
         <v>1</v>
       </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6654,11 +6419,6 @@
       <c r="U48" t="b">
         <v>1</v>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6746,11 +6506,6 @@
       <c r="U49" t="b">
         <v>1</v>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6838,11 +6593,6 @@
       <c r="U50" t="b">
         <v>1</v>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6930,11 +6680,6 @@
       <c r="U51" t="b">
         <v>1</v>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7022,11 +6767,6 @@
       <c r="U52" t="b">
         <v>0</v>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7114,11 +6854,6 @@
       <c r="U53" t="b">
         <v>1</v>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7206,11 +6941,6 @@
       <c r="U54" t="b">
         <v>1</v>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7298,11 +7028,6 @@
       <c r="U55" t="b">
         <v>1</v>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7390,11 +7115,6 @@
       <c r="U56" t="b">
         <v>1</v>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7482,11 +7202,6 @@
       <c r="U57" t="b">
         <v>1</v>
       </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7574,11 +7289,6 @@
       <c r="U58" t="b">
         <v>1</v>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7666,11 +7376,6 @@
       <c r="U59" t="b">
         <v>1</v>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7758,11 +7463,6 @@
       <c r="U60" t="b">
         <v>1</v>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7850,11 +7550,6 @@
       <c r="U61" t="b">
         <v>1</v>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7942,11 +7637,6 @@
       <c r="U62" t="b">
         <v>1</v>
       </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8034,11 +7724,6 @@
       <c r="U63" t="b">
         <v>0</v>
       </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8126,11 +7811,6 @@
       <c r="U64" t="b">
         <v>1</v>
       </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8218,11 +7898,6 @@
       <c r="U65" t="b">
         <v>1</v>
       </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8310,11 +7985,6 @@
       <c r="U66" t="b">
         <v>0</v>
       </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8402,11 +8072,6 @@
       <c r="U67" t="b">
         <v>1</v>
       </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8494,11 +8159,6 @@
       <c r="U68" t="b">
         <v>1</v>
       </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8586,11 +8246,6 @@
       <c r="U69" t="b">
         <v>1</v>
       </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8678,11 +8333,6 @@
       <c r="U70" t="b">
         <v>1</v>
       </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8770,11 +8420,6 @@
       <c r="U71" t="b">
         <v>1</v>
       </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8862,11 +8507,6 @@
       <c r="U72" t="b">
         <v>1</v>
       </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8954,11 +8594,6 @@
       <c r="U73" t="b">
         <v>1</v>
       </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9046,11 +8681,6 @@
       <c r="U74" t="b">
         <v>1</v>
       </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9138,11 +8768,6 @@
       <c r="U75" t="b">
         <v>1</v>
       </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9230,11 +8855,6 @@
       <c r="U76" t="b">
         <v>0</v>
       </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9322,11 +8942,6 @@
       <c r="U77" t="b">
         <v>1</v>
       </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9414,11 +9029,6 @@
       <c r="U78" t="b">
         <v>0</v>
       </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9506,11 +9116,6 @@
       <c r="U79" t="b">
         <v>1</v>
       </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9598,11 +9203,6 @@
       <c r="U80" t="b">
         <v>1</v>
       </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9690,11 +9290,6 @@
       <c r="U81" t="b">
         <v>1</v>
       </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9782,11 +9377,6 @@
       <c r="U82" t="b">
         <v>1</v>
       </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9874,11 +9464,6 @@
       <c r="U83" t="b">
         <v>1</v>
       </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9966,11 +9551,6 @@
       <c r="U84" t="b">
         <v>1</v>
       </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10058,11 +9638,6 @@
       <c r="U85" t="b">
         <v>0</v>
       </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10150,11 +9725,6 @@
       <c r="U86" t="b">
         <v>1</v>
       </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10242,11 +9812,6 @@
       <c r="U87" t="b">
         <v>1</v>
       </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10334,11 +9899,6 @@
       <c r="U88" t="b">
         <v>0</v>
       </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10426,11 +9986,6 @@
       <c r="U89" t="b">
         <v>1</v>
       </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10518,11 +10073,6 @@
       <c r="U90" t="b">
         <v>0</v>
       </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10610,11 +10160,6 @@
       <c r="U91" t="b">
         <v>1</v>
       </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10702,11 +10247,6 @@
       <c r="U92" t="b">
         <v>1</v>
       </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10794,11 +10334,6 @@
       <c r="U93" t="b">
         <v>1</v>
       </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10886,11 +10421,6 @@
       <c r="U94" t="b">
         <v>0</v>
       </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10978,11 +10508,6 @@
       <c r="U95" t="b">
         <v>1</v>
       </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11070,11 +10595,6 @@
       <c r="U96" t="b">
         <v>1</v>
       </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11162,11 +10682,6 @@
       <c r="U97" t="b">
         <v>0</v>
       </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11254,11 +10769,6 @@
       <c r="U98" t="b">
         <v>0</v>
       </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11346,11 +10856,6 @@
       <c r="U99" t="b">
         <v>1</v>
       </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11438,11 +10943,6 @@
       <c r="U100" t="b">
         <v>1</v>
       </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11530,11 +11030,6 @@
       <c r="U101" t="b">
         <v>1</v>
       </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11622,11 +11117,6 @@
       <c r="U102" t="b">
         <v>1</v>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11714,11 +11204,6 @@
       <c r="U103" t="b">
         <v>1</v>
       </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11806,11 +11291,6 @@
       <c r="U104" t="b">
         <v>1</v>
       </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11898,11 +11378,6 @@
       <c r="U105" t="b">
         <v>0</v>
       </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11990,11 +11465,6 @@
       <c r="U106" t="b">
         <v>1</v>
       </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -12082,11 +11552,6 @@
       <c r="U107" t="b">
         <v>1</v>
       </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -12174,11 +11639,6 @@
       <c r="U108" t="b">
         <v>1</v>
       </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -12266,11 +11726,6 @@
       <c r="U109" t="b">
         <v>1</v>
       </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -12358,11 +11813,6 @@
       <c r="U110" t="b">
         <v>1</v>
       </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -12450,11 +11900,6 @@
       <c r="U111" t="b">
         <v>1</v>
       </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -12542,11 +11987,6 @@
       <c r="U112" t="b">
         <v>1</v>
       </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -12634,11 +12074,6 @@
       <c r="U113" t="b">
         <v>1</v>
       </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -12726,11 +12161,6 @@
       <c r="U114" t="b">
         <v>0</v>
       </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12818,11 +12248,6 @@
       <c r="U115" t="b">
         <v>1</v>
       </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -12910,11 +12335,6 @@
       <c r="U116" t="b">
         <v>1</v>
       </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -13002,11 +12422,6 @@
       <c r="U117" t="b">
         <v>1</v>
       </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -13094,11 +12509,6 @@
       <c r="U118" t="b">
         <v>1</v>
       </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -13186,11 +12596,6 @@
       <c r="U119" t="b">
         <v>0</v>
       </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -13278,11 +12683,6 @@
       <c r="U120" t="b">
         <v>0</v>
       </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -13370,11 +12770,6 @@
       <c r="U121" t="b">
         <v>1</v>
       </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -13462,11 +12857,6 @@
       <c r="U122" t="b">
         <v>1</v>
       </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -13554,11 +12944,6 @@
       <c r="U123" t="b">
         <v>0</v>
       </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -13646,11 +13031,6 @@
       <c r="U124" t="b">
         <v>0</v>
       </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -13738,11 +13118,6 @@
       <c r="U125" t="b">
         <v>1</v>
       </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13830,11 +13205,6 @@
       <c r="U126" t="b">
         <v>1</v>
       </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13922,11 +13292,6 @@
       <c r="U127" t="b">
         <v>1</v>
       </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14014,11 +13379,6 @@
       <c r="U128" t="b">
         <v>0</v>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -14106,11 +13466,6 @@
       <c r="U129" t="b">
         <v>1</v>
       </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -14198,11 +13553,6 @@
       <c r="U130" t="b">
         <v>1</v>
       </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -14290,11 +13640,6 @@
       <c r="U131" t="b">
         <v>0</v>
       </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -14382,11 +13727,6 @@
       <c r="U132" t="b">
         <v>1</v>
       </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14474,11 +13814,6 @@
       <c r="U133" t="b">
         <v>1</v>
       </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -14566,11 +13901,6 @@
       <c r="U134" t="b">
         <v>1</v>
       </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14658,11 +13988,6 @@
       <c r="U135" t="b">
         <v>1</v>
       </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14750,11 +14075,6 @@
       <c r="U136" t="b">
         <v>1</v>
       </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14842,11 +14162,6 @@
       <c r="U137" t="b">
         <v>1</v>
       </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14934,11 +14249,6 @@
       <c r="U138" t="b">
         <v>1</v>
       </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -15026,11 +14336,6 @@
       <c r="U139" t="b">
         <v>1</v>
       </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -15118,11 +14423,6 @@
       <c r="U140" t="b">
         <v>1</v>
       </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -15210,11 +14510,6 @@
       <c r="U141" t="b">
         <v>1</v>
       </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -15302,11 +14597,6 @@
       <c r="U142" t="b">
         <v>1</v>
       </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -15394,11 +14684,6 @@
       <c r="U143" t="b">
         <v>1</v>
       </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -15486,11 +14771,6 @@
       <c r="U144" t="b">
         <v>0</v>
       </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15578,11 +14858,6 @@
       <c r="U145" t="b">
         <v>1</v>
       </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15670,11 +14945,6 @@
       <c r="U146" t="b">
         <v>0</v>
       </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15762,11 +15032,6 @@
       <c r="U147" t="b">
         <v>1</v>
       </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15854,11 +15119,6 @@
       <c r="U148" t="b">
         <v>1</v>
       </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15946,11 +15206,6 @@
       <c r="U149" t="b">
         <v>0</v>
       </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -16038,11 +15293,6 @@
       <c r="U150" t="b">
         <v>1</v>
       </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -16130,11 +15380,6 @@
       <c r="U151" t="b">
         <v>1</v>
       </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -16222,11 +15467,6 @@
       <c r="U152" t="b">
         <v>1</v>
       </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -16314,11 +15554,6 @@
       <c r="U153" t="b">
         <v>1</v>
       </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -16406,11 +15641,6 @@
       <c r="U154" t="b">
         <v>1</v>
       </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -16498,11 +15728,6 @@
       <c r="U155" t="b">
         <v>1</v>
       </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -16590,11 +15815,6 @@
       <c r="U156" t="b">
         <v>1</v>
       </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -16682,11 +15902,6 @@
       <c r="U157" t="b">
         <v>1</v>
       </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -16774,11 +15989,6 @@
       <c r="U158" t="b">
         <v>1</v>
       </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16866,11 +16076,6 @@
       <c r="U159" t="b">
         <v>0</v>
       </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16958,11 +16163,6 @@
       <c r="U160" t="b">
         <v>1</v>
       </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -17050,11 +16250,6 @@
       <c r="U161" t="b">
         <v>0</v>
       </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -17142,11 +16337,6 @@
       <c r="U162" t="b">
         <v>1</v>
       </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -17234,11 +16424,6 @@
       <c r="U163" t="b">
         <v>0</v>
       </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -17326,11 +16511,6 @@
       <c r="U164" t="b">
         <v>1</v>
       </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -17418,11 +16598,6 @@
       <c r="U165" t="b">
         <v>1</v>
       </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -17510,11 +16685,6 @@
       <c r="U166" t="b">
         <v>0</v>
       </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -17602,11 +16772,6 @@
       <c r="U167" t="b">
         <v>0</v>
       </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -17694,11 +16859,6 @@
       <c r="U168" t="b">
         <v>1</v>
       </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -17786,11 +16946,6 @@
       <c r="U169" t="b">
         <v>1</v>
       </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -17878,11 +17033,6 @@
       <c r="U170" t="b">
         <v>0</v>
       </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -17970,11 +17120,6 @@
       <c r="U171" t="b">
         <v>1</v>
       </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -18062,11 +17207,6 @@
       <c r="U172" t="b">
         <v>1</v>
       </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -18154,11 +17294,6 @@
       <c r="U173" t="b">
         <v>1</v>
       </c>
-      <c r="V173" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -18246,11 +17381,6 @@
       <c r="U174" t="b">
         <v>1</v>
       </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -18338,11 +17468,6 @@
       <c r="U175" t="b">
         <v>1</v>
       </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -18430,11 +17555,6 @@
       <c r="U176" t="b">
         <v>0</v>
       </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -18522,11 +17642,6 @@
       <c r="U177" t="b">
         <v>1</v>
       </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -18614,11 +17729,6 @@
       <c r="U178" t="b">
         <v>0</v>
       </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -18706,11 +17816,6 @@
       <c r="U179" t="b">
         <v>1</v>
       </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -18798,11 +17903,6 @@
       <c r="U180" t="b">
         <v>1</v>
       </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -18890,11 +17990,6 @@
       <c r="U181" t="b">
         <v>1</v>
       </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -18982,11 +18077,6 @@
       <c r="U182" t="b">
         <v>1</v>
       </c>
-      <c r="V182" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -19074,11 +18164,6 @@
       <c r="U183" t="b">
         <v>1</v>
       </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -19166,11 +18251,6 @@
       <c r="U184" t="b">
         <v>1</v>
       </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -19258,11 +18338,6 @@
       <c r="U185" t="b">
         <v>0</v>
       </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -19350,11 +18425,6 @@
       <c r="U186" t="b">
         <v>1</v>
       </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -19442,11 +18512,6 @@
       <c r="U187" t="b">
         <v>0</v>
       </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -19534,11 +18599,6 @@
       <c r="U188" t="b">
         <v>0</v>
       </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -19626,11 +18686,6 @@
       <c r="U189" t="b">
         <v>0</v>
       </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -19718,11 +18773,6 @@
       <c r="U190" t="b">
         <v>1</v>
       </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -19810,11 +18860,6 @@
       <c r="U191" t="b">
         <v>0</v>
       </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -19902,11 +18947,6 @@
       <c r="U192" t="b">
         <v>1</v>
       </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -19994,11 +19034,6 @@
       <c r="U193" t="b">
         <v>1</v>
       </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -20086,11 +19121,6 @@
       <c r="U194" t="b">
         <v>1</v>
       </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -20178,11 +19208,6 @@
       <c r="U195" t="b">
         <v>1</v>
       </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -20270,11 +19295,6 @@
       <c r="U196" t="b">
         <v>1</v>
       </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -20362,11 +19382,6 @@
       <c r="U197" t="b">
         <v>1</v>
       </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -20454,11 +19469,6 @@
       <c r="U198" t="b">
         <v>1</v>
       </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -20546,11 +19556,6 @@
       <c r="U199" t="b">
         <v>1</v>
       </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -20638,11 +19643,6 @@
       <c r="U200" t="b">
         <v>1</v>
       </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -20730,11 +19730,6 @@
       <c r="U201" t="b">
         <v>0</v>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -20822,11 +19817,6 @@
       <c r="U202" t="b">
         <v>1</v>
       </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -20914,11 +19904,6 @@
       <c r="U203" t="b">
         <v>0</v>
       </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -21006,11 +19991,6 @@
       <c r="U204" t="b">
         <v>1</v>
       </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -21098,11 +20078,6 @@
       <c r="U205" t="b">
         <v>0</v>
       </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -21190,11 +20165,6 @@
       <c r="U206" t="b">
         <v>1</v>
       </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -21282,11 +20252,6 @@
       <c r="U207" t="b">
         <v>0</v>
       </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -21374,11 +20339,6 @@
       <c r="U208" t="b">
         <v>0</v>
       </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -21466,11 +20426,6 @@
       <c r="U209" t="b">
         <v>1</v>
       </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -21558,11 +20513,6 @@
       <c r="U210" t="b">
         <v>0</v>
       </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -21650,11 +20600,6 @@
       <c r="U211" t="b">
         <v>0</v>
       </c>
-      <c r="V211" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -21742,11 +20687,6 @@
       <c r="U212" t="b">
         <v>0</v>
       </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -21834,11 +20774,6 @@
       <c r="U213" t="b">
         <v>0</v>
       </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -21926,11 +20861,6 @@
       <c r="U214" t="b">
         <v>1</v>
       </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -22018,11 +20948,6 @@
       <c r="U215" t="b">
         <v>1</v>
       </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -22110,11 +21035,6 @@
       <c r="U216" t="b">
         <v>1</v>
       </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -22202,11 +21122,6 @@
       <c r="U217" t="b">
         <v>1</v>
       </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -22294,11 +21209,6 @@
       <c r="U218" t="b">
         <v>0</v>
       </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -22386,11 +21296,6 @@
       <c r="U219" t="b">
         <v>1</v>
       </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -22478,11 +21383,6 @@
       <c r="U220" t="b">
         <v>1</v>
       </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -22570,11 +21470,6 @@
       <c r="U221" t="b">
         <v>1</v>
       </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -22662,11 +21557,6 @@
       <c r="U222" t="b">
         <v>1</v>
       </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -22754,11 +21644,6 @@
       <c r="U223" t="b">
         <v>1</v>
       </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -22846,11 +21731,6 @@
       <c r="U224" t="b">
         <v>0</v>
       </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -22938,11 +21818,6 @@
       <c r="U225" t="b">
         <v>1</v>
       </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -23030,11 +21905,6 @@
       <c r="U226" t="b">
         <v>1</v>
       </c>
-      <c r="V226" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -23122,11 +21992,6 @@
       <c r="U227" t="b">
         <v>1</v>
       </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -23214,11 +22079,6 @@
       <c r="U228" t="b">
         <v>1</v>
       </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -23306,11 +22166,6 @@
       <c r="U229" t="b">
         <v>0</v>
       </c>
-      <c r="V229" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -23398,11 +22253,6 @@
       <c r="U230" t="b">
         <v>1</v>
       </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -23490,11 +22340,6 @@
       <c r="U231" t="b">
         <v>1</v>
       </c>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -23582,11 +22427,6 @@
       <c r="U232" t="b">
         <v>1</v>
       </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -23674,11 +22514,6 @@
       <c r="U233" t="b">
         <v>1</v>
       </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -23766,11 +22601,6 @@
       <c r="U234" t="b">
         <v>1</v>
       </c>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -23858,11 +22688,6 @@
       <c r="U235" t="b">
         <v>0</v>
       </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -23950,11 +22775,6 @@
       <c r="U236" t="b">
         <v>0</v>
       </c>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -24042,11 +22862,6 @@
       <c r="U237" t="b">
         <v>1</v>
       </c>
-      <c r="V237" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -24134,11 +22949,6 @@
       <c r="U238" t="b">
         <v>1</v>
       </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -24226,11 +23036,6 @@
       <c r="U239" t="b">
         <v>1</v>
       </c>
-      <c r="V239" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -24318,11 +23123,6 @@
       <c r="U240" t="b">
         <v>1</v>
       </c>
-      <c r="V240" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -24410,11 +23210,6 @@
       <c r="U241" t="b">
         <v>0</v>
       </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -24502,11 +23297,6 @@
       <c r="U242" t="b">
         <v>1</v>
       </c>
-      <c r="V242" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -24594,11 +23384,6 @@
       <c r="U243" t="b">
         <v>1</v>
       </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -24686,11 +23471,6 @@
       <c r="U244" t="b">
         <v>1</v>
       </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -24778,11 +23558,6 @@
       <c r="U245" t="b">
         <v>1</v>
       </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -24870,11 +23645,6 @@
       <c r="U246" t="b">
         <v>1</v>
       </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -24962,11 +23732,6 @@
       <c r="U247" t="b">
         <v>1</v>
       </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -25054,11 +23819,6 @@
       <c r="U248" t="b">
         <v>1</v>
       </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -25146,11 +23906,6 @@
       <c r="U249" t="b">
         <v>1</v>
       </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -25238,11 +23993,6 @@
       <c r="U250" t="b">
         <v>0</v>
       </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -25330,11 +24080,6 @@
       <c r="U251" t="b">
         <v>0</v>
       </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -25422,11 +24167,6 @@
       <c r="U252" t="b">
         <v>0</v>
       </c>
-      <c r="V252" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -25514,11 +24254,6 @@
       <c r="U253" t="b">
         <v>1</v>
       </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -25606,11 +24341,6 @@
       <c r="U254" t="b">
         <v>1</v>
       </c>
-      <c r="V254" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -25698,11 +24428,6 @@
       <c r="U255" t="b">
         <v>1</v>
       </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -25790,11 +24515,6 @@
       <c r="U256" t="b">
         <v>1</v>
       </c>
-      <c r="V256" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -25882,11 +24602,6 @@
       <c r="U257" t="b">
         <v>1</v>
       </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -25974,11 +24689,6 @@
       <c r="U258" t="b">
         <v>1</v>
       </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -26066,11 +24776,6 @@
       <c r="U259" t="b">
         <v>1</v>
       </c>
-      <c r="V259" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -26158,11 +24863,6 @@
       <c r="U260" t="b">
         <v>1</v>
       </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -26250,11 +24950,6 @@
       <c r="U261" t="b">
         <v>1</v>
       </c>
-      <c r="V261" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -26342,11 +25037,6 @@
       <c r="U262" t="b">
         <v>1</v>
       </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -26434,11 +25124,6 @@
       <c r="U263" t="b">
         <v>1</v>
       </c>
-      <c r="V263" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -26526,11 +25211,6 @@
       <c r="U264" t="b">
         <v>1</v>
       </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -26618,11 +25298,6 @@
       <c r="U265" t="b">
         <v>1</v>
       </c>
-      <c r="V265" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -26710,11 +25385,6 @@
       <c r="U266" t="b">
         <v>1</v>
       </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -26802,11 +25472,6 @@
       <c r="U267" t="b">
         <v>1</v>
       </c>
-      <c r="V267" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -26894,11 +25559,6 @@
       <c r="U268" t="b">
         <v>1</v>
       </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -26986,11 +25646,6 @@
       <c r="U269" t="b">
         <v>1</v>
       </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -27078,11 +25733,6 @@
       <c r="U270" t="b">
         <v>0</v>
       </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -27170,11 +25820,6 @@
       <c r="U271" t="b">
         <v>1</v>
       </c>
-      <c r="V271" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -27262,11 +25907,6 @@
       <c r="U272" t="b">
         <v>1</v>
       </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -27354,11 +25994,6 @@
       <c r="U273" t="b">
         <v>0</v>
       </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -27446,11 +26081,6 @@
       <c r="U274" t="b">
         <v>1</v>
       </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -27538,11 +26168,6 @@
       <c r="U275" t="b">
         <v>1</v>
       </c>
-      <c r="V275" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -27630,11 +26255,6 @@
       <c r="U276" t="b">
         <v>0</v>
       </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -27722,11 +26342,6 @@
       <c r="U277" t="b">
         <v>1</v>
       </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -27814,11 +26429,6 @@
       <c r="U278" t="b">
         <v>0</v>
       </c>
-      <c r="V278" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -27906,11 +26516,6 @@
       <c r="U279" t="b">
         <v>1</v>
       </c>
-      <c r="V279" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -27998,11 +26603,6 @@
       <c r="U280" t="b">
         <v>1</v>
       </c>
-      <c r="V280" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -28090,11 +26690,6 @@
       <c r="U281" t="b">
         <v>1</v>
       </c>
-      <c r="V281" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -28182,11 +26777,6 @@
       <c r="U282" t="b">
         <v>1</v>
       </c>
-      <c r="V282" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -28274,11 +26864,6 @@
       <c r="U283" t="b">
         <v>1</v>
       </c>
-      <c r="V283" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -28366,11 +26951,6 @@
       <c r="U284" t="b">
         <v>0</v>
       </c>
-      <c r="V284" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -28458,11 +27038,6 @@
       <c r="U285" t="b">
         <v>0</v>
       </c>
-      <c r="V285" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -28550,11 +27125,6 @@
       <c r="U286" t="b">
         <v>0</v>
       </c>
-      <c r="V286" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -28642,11 +27212,6 @@
       <c r="U287" t="b">
         <v>1</v>
       </c>
-      <c r="V287" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -28734,11 +27299,6 @@
       <c r="U288" t="b">
         <v>0</v>
       </c>
-      <c r="V288" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -28826,11 +27386,6 @@
       <c r="U289" t="b">
         <v>1</v>
       </c>
-      <c r="V289" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -28918,11 +27473,6 @@
       <c r="U290" t="b">
         <v>1</v>
       </c>
-      <c r="V290" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -29010,11 +27560,6 @@
       <c r="U291" t="b">
         <v>1</v>
       </c>
-      <c r="V291" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -29102,11 +27647,6 @@
       <c r="U292" t="b">
         <v>1</v>
       </c>
-      <c r="V292" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -29194,11 +27734,6 @@
       <c r="U293" t="b">
         <v>1</v>
       </c>
-      <c r="V293" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -29286,11 +27821,6 @@
       <c r="U294" t="b">
         <v>1</v>
       </c>
-      <c r="V294" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -29378,11 +27908,6 @@
       <c r="U295" t="b">
         <v>1</v>
       </c>
-      <c r="V295" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -29470,11 +27995,6 @@
       <c r="U296" t="b">
         <v>0</v>
       </c>
-      <c r="V296" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -29562,11 +28082,6 @@
       <c r="U297" t="b">
         <v>0</v>
       </c>
-      <c r="V297" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -29654,11 +28169,6 @@
       <c r="U298" t="b">
         <v>1</v>
       </c>
-      <c r="V298" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -29746,11 +28256,6 @@
       <c r="U299" t="b">
         <v>1</v>
       </c>
-      <c r="V299" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -29838,11 +28343,6 @@
       <c r="U300" t="b">
         <v>1</v>
       </c>
-      <c r="V300" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -29930,11 +28430,6 @@
       <c r="U301" t="b">
         <v>1</v>
       </c>
-      <c r="V301" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -30022,11 +28517,6 @@
       <c r="U302" t="b">
         <v>1</v>
       </c>
-      <c r="V302" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -30114,11 +28604,6 @@
       <c r="U303" t="b">
         <v>1</v>
       </c>
-      <c r="V303" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -30206,11 +28691,6 @@
       <c r="U304" t="b">
         <v>1</v>
       </c>
-      <c r="V304" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -30298,11 +28778,6 @@
       <c r="U305" t="b">
         <v>0</v>
       </c>
-      <c r="V305" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -30390,11 +28865,6 @@
       <c r="U306" t="b">
         <v>1</v>
       </c>
-      <c r="V306" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -30482,11 +28952,6 @@
       <c r="U307" t="b">
         <v>1</v>
       </c>
-      <c r="V307" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -30574,11 +29039,6 @@
       <c r="U308" t="b">
         <v>0</v>
       </c>
-      <c r="V308" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -30666,11 +29126,6 @@
       <c r="U309" t="b">
         <v>1</v>
       </c>
-      <c r="V309" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -30758,11 +29213,6 @@
       <c r="U310" t="b">
         <v>1</v>
       </c>
-      <c r="V310" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -30850,11 +29300,6 @@
       <c r="U311" t="b">
         <v>1</v>
       </c>
-      <c r="V311" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -30942,11 +29387,6 @@
       <c r="U312" t="b">
         <v>0</v>
       </c>
-      <c r="V312" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -31034,11 +29474,6 @@
       <c r="U313" t="b">
         <v>1</v>
       </c>
-      <c r="V313" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -31126,11 +29561,6 @@
       <c r="U314" t="b">
         <v>1</v>
       </c>
-      <c r="V314" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -31218,11 +29648,6 @@
       <c r="U315" t="b">
         <v>1</v>
       </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -31310,11 +29735,6 @@
       <c r="U316" t="b">
         <v>1</v>
       </c>
-      <c r="V316" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -31402,11 +29822,6 @@
       <c r="U317" t="b">
         <v>1</v>
       </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -31494,11 +29909,6 @@
       <c r="U318" t="b">
         <v>1</v>
       </c>
-      <c r="V318" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -31586,11 +29996,6 @@
       <c r="U319" t="b">
         <v>1</v>
       </c>
-      <c r="V319" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -31678,11 +30083,6 @@
       <c r="U320" t="b">
         <v>1</v>
       </c>
-      <c r="V320" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -31770,11 +30170,6 @@
       <c r="U321" t="b">
         <v>1</v>
       </c>
-      <c r="V321" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -31862,11 +30257,6 @@
       <c r="U322" t="b">
         <v>1</v>
       </c>
-      <c r="V322" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -31954,11 +30344,6 @@
       <c r="U323" t="b">
         <v>0</v>
       </c>
-      <c r="V323" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -32046,11 +30431,6 @@
       <c r="U324" t="b">
         <v>0</v>
       </c>
-      <c r="V324" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -32138,11 +30518,6 @@
       <c r="U325" t="b">
         <v>1</v>
       </c>
-      <c r="V325" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -32230,11 +30605,6 @@
       <c r="U326" t="b">
         <v>1</v>
       </c>
-      <c r="V326" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -32322,11 +30692,6 @@
       <c r="U327" t="b">
         <v>1</v>
       </c>
-      <c r="V327" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -32414,11 +30779,6 @@
       <c r="U328" t="b">
         <v>1</v>
       </c>
-      <c r="V328" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -32506,11 +30866,6 @@
       <c r="U329" t="b">
         <v>1</v>
       </c>
-      <c r="V329" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -32598,11 +30953,6 @@
       <c r="U330" t="b">
         <v>0</v>
       </c>
-      <c r="V330" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -32690,11 +31040,6 @@
       <c r="U331" t="b">
         <v>1</v>
       </c>
-      <c r="V331" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -32782,11 +31127,6 @@
       <c r="U332" t="b">
         <v>1</v>
       </c>
-      <c r="V332" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -32874,11 +31214,6 @@
       <c r="U333" t="b">
         <v>1</v>
       </c>
-      <c r="V333" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -32966,11 +31301,6 @@
       <c r="U334" t="b">
         <v>1</v>
       </c>
-      <c r="V334" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -33058,11 +31388,6 @@
       <c r="U335" t="b">
         <v>1</v>
       </c>
-      <c r="V335" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -33150,11 +31475,6 @@
       <c r="U336" t="b">
         <v>1</v>
       </c>
-      <c r="V336" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -33242,11 +31562,6 @@
       <c r="U337" t="b">
         <v>1</v>
       </c>
-      <c r="V337" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -33334,11 +31649,6 @@
       <c r="U338" t="b">
         <v>1</v>
       </c>
-      <c r="V338" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -33426,11 +31736,6 @@
       <c r="U339" t="b">
         <v>1</v>
       </c>
-      <c r="V339" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -33518,11 +31823,6 @@
       <c r="U340" t="b">
         <v>0</v>
       </c>
-      <c r="V340" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -33610,11 +31910,6 @@
       <c r="U341" t="b">
         <v>1</v>
       </c>
-      <c r="V341" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -33702,11 +31997,6 @@
       <c r="U342" t="b">
         <v>1</v>
       </c>
-      <c r="V342" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -33794,11 +32084,6 @@
       <c r="U343" t="b">
         <v>1</v>
       </c>
-      <c r="V343" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -33886,11 +32171,6 @@
       <c r="U344" t="b">
         <v>1</v>
       </c>
-      <c r="V344" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -33978,11 +32258,6 @@
       <c r="U345" t="b">
         <v>0</v>
       </c>
-      <c r="V345" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -34070,11 +32345,6 @@
       <c r="U346" t="b">
         <v>0</v>
       </c>
-      <c r="V346" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -34162,11 +32432,6 @@
       <c r="U347" t="b">
         <v>1</v>
       </c>
-      <c r="V347" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -34254,11 +32519,6 @@
       <c r="U348" t="b">
         <v>0</v>
       </c>
-      <c r="V348" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -34346,11 +32606,6 @@
       <c r="U349" t="b">
         <v>1</v>
       </c>
-      <c r="V349" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -34438,11 +32693,6 @@
       <c r="U350" t="b">
         <v>0</v>
       </c>
-      <c r="V350" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -34530,11 +32780,6 @@
       <c r="U351" t="b">
         <v>1</v>
       </c>
-      <c r="V351" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -34622,11 +32867,6 @@
       <c r="U352" t="b">
         <v>0</v>
       </c>
-      <c r="V352" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -34714,11 +32954,6 @@
       <c r="U353" t="b">
         <v>1</v>
       </c>
-      <c r="V353" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -34806,11 +33041,6 @@
       <c r="U354" t="b">
         <v>0</v>
       </c>
-      <c r="V354" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -34898,11 +33128,6 @@
       <c r="U355" t="b">
         <v>1</v>
       </c>
-      <c r="V355" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -34990,11 +33215,6 @@
       <c r="U356" t="b">
         <v>0</v>
       </c>
-      <c r="V356" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -35082,11 +33302,6 @@
       <c r="U357" t="b">
         <v>0</v>
       </c>
-      <c r="V357" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -35174,11 +33389,6 @@
       <c r="U358" t="b">
         <v>1</v>
       </c>
-      <c r="V358" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -35266,11 +33476,6 @@
       <c r="U359" t="b">
         <v>0</v>
       </c>
-      <c r="V359" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -35358,11 +33563,6 @@
       <c r="U360" t="b">
         <v>0</v>
       </c>
-      <c r="V360" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -35450,11 +33650,6 @@
       <c r="U361" t="b">
         <v>1</v>
       </c>
-      <c r="V361" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -35542,11 +33737,6 @@
       <c r="U362" t="b">
         <v>0</v>
       </c>
-      <c r="V362" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -35634,11 +33824,6 @@
       <c r="U363" t="b">
         <v>0</v>
       </c>
-      <c r="V363" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -35726,11 +33911,6 @@
       <c r="U364" t="b">
         <v>1</v>
       </c>
-      <c r="V364" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -35818,11 +33998,6 @@
       <c r="U365" t="b">
         <v>1</v>
       </c>
-      <c r="V365" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -35910,11 +34085,6 @@
       <c r="U366" t="b">
         <v>1</v>
       </c>
-      <c r="V366" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -36002,11 +34172,6 @@
       <c r="U367" t="b">
         <v>1</v>
       </c>
-      <c r="V367" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -36094,11 +34259,6 @@
       <c r="U368" t="b">
         <v>1</v>
       </c>
-      <c r="V368" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -36186,11 +34346,6 @@
       <c r="U369" t="b">
         <v>1</v>
       </c>
-      <c r="V369" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -36278,11 +34433,6 @@
       <c r="U370" t="b">
         <v>0</v>
       </c>
-      <c r="V370" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -36370,11 +34520,6 @@
       <c r="U371" t="b">
         <v>0</v>
       </c>
-      <c r="V371" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -36462,11 +34607,6 @@
       <c r="U372" t="b">
         <v>1</v>
       </c>
-      <c r="V372" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -36554,11 +34694,6 @@
       <c r="U373" t="b">
         <v>1</v>
       </c>
-      <c r="V373" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -36646,11 +34781,6 @@
       <c r="U374" t="b">
         <v>1</v>
       </c>
-      <c r="V374" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -36738,11 +34868,6 @@
       <c r="U375" t="b">
         <v>1</v>
       </c>
-      <c r="V375" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -36830,11 +34955,6 @@
       <c r="U376" t="b">
         <v>1</v>
       </c>
-      <c r="V376" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -36922,11 +35042,6 @@
       <c r="U377" t="b">
         <v>0</v>
       </c>
-      <c r="V377" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -37014,11 +35129,6 @@
       <c r="U378" t="b">
         <v>1</v>
       </c>
-      <c r="V378" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -37106,11 +35216,6 @@
       <c r="U379" t="b">
         <v>1</v>
       </c>
-      <c r="V379" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -37198,11 +35303,6 @@
       <c r="U380" t="b">
         <v>1</v>
       </c>
-      <c r="V380" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -37290,11 +35390,6 @@
       <c r="U381" t="b">
         <v>0</v>
       </c>
-      <c r="V381" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -37382,11 +35477,6 @@
       <c r="U382" t="b">
         <v>1</v>
       </c>
-      <c r="V382" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -37474,11 +35564,6 @@
       <c r="U383" t="b">
         <v>1</v>
       </c>
-      <c r="V383" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -37566,11 +35651,6 @@
       <c r="U384" t="b">
         <v>1</v>
       </c>
-      <c r="V384" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -37658,11 +35738,6 @@
       <c r="U385" t="b">
         <v>1</v>
       </c>
-      <c r="V385" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -37750,11 +35825,6 @@
       <c r="U386" t="b">
         <v>1</v>
       </c>
-      <c r="V386" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -37842,11 +35912,6 @@
       <c r="U387" t="b">
         <v>1</v>
       </c>
-      <c r="V387" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -37934,11 +35999,6 @@
       <c r="U388" t="b">
         <v>1</v>
       </c>
-      <c r="V388" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -38026,11 +36086,6 @@
       <c r="U389" t="b">
         <v>1</v>
       </c>
-      <c r="V389" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -38118,11 +36173,6 @@
       <c r="U390" t="b">
         <v>1</v>
       </c>
-      <c r="V390" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -38210,11 +36260,6 @@
       <c r="U391" t="b">
         <v>1</v>
       </c>
-      <c r="V391" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -38302,11 +36347,6 @@
       <c r="U392" t="b">
         <v>1</v>
       </c>
-      <c r="V392" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -38394,11 +36434,6 @@
       <c r="U393" t="b">
         <v>1</v>
       </c>
-      <c r="V393" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -38486,11 +36521,6 @@
       <c r="U394" t="b">
         <v>0</v>
       </c>
-      <c r="V394" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -38578,11 +36608,6 @@
       <c r="U395" t="b">
         <v>1</v>
       </c>
-      <c r="V395" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -38670,11 +36695,6 @@
       <c r="U396" t="b">
         <v>1</v>
       </c>
-      <c r="V396" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -38762,11 +36782,6 @@
       <c r="U397" t="b">
         <v>0</v>
       </c>
-      <c r="V397" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -38854,11 +36869,6 @@
       <c r="U398" t="b">
         <v>1</v>
       </c>
-      <c r="V398" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -38946,11 +36956,6 @@
       <c r="U399" t="b">
         <v>1</v>
       </c>
-      <c r="V399" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -39038,11 +37043,6 @@
       <c r="U400" t="b">
         <v>1</v>
       </c>
-      <c r="V400" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -39130,11 +37130,6 @@
       <c r="U401" t="b">
         <v>1</v>
       </c>
-      <c r="V401" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -39222,11 +37217,6 @@
       <c r="U402" t="b">
         <v>1</v>
       </c>
-      <c r="V402" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -39314,11 +37304,6 @@
       <c r="U403" t="b">
         <v>1</v>
       </c>
-      <c r="V403" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -39406,11 +37391,6 @@
       <c r="U404" t="b">
         <v>0</v>
       </c>
-      <c r="V404" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -39498,11 +37478,6 @@
       <c r="U405" t="b">
         <v>1</v>
       </c>
-      <c r="V405" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -39590,11 +37565,6 @@
       <c r="U406" t="b">
         <v>0</v>
       </c>
-      <c r="V406" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -39682,11 +37652,6 @@
       <c r="U407" t="b">
         <v>1</v>
       </c>
-      <c r="V407" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -39774,11 +37739,6 @@
       <c r="U408" t="b">
         <v>1</v>
       </c>
-      <c r="V408" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -39866,11 +37826,6 @@
       <c r="U409" t="b">
         <v>1</v>
       </c>
-      <c r="V409" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -39958,11 +37913,6 @@
       <c r="U410" t="b">
         <v>1</v>
       </c>
-      <c r="V410" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -40050,11 +38000,6 @@
       <c r="U411" t="b">
         <v>0</v>
       </c>
-      <c r="V411" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -40142,11 +38087,6 @@
       <c r="U412" t="b">
         <v>1</v>
       </c>
-      <c r="V412" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -40234,11 +38174,6 @@
       <c r="U413" t="b">
         <v>1</v>
       </c>
-      <c r="V413" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -40326,11 +38261,6 @@
       <c r="U414" t="b">
         <v>1</v>
       </c>
-      <c r="V414" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -40418,11 +38348,6 @@
       <c r="U415" t="b">
         <v>1</v>
       </c>
-      <c r="V415" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -40510,11 +38435,6 @@
       <c r="U416" t="b">
         <v>0</v>
       </c>
-      <c r="V416" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -40602,11 +38522,6 @@
       <c r="U417" t="b">
         <v>1</v>
       </c>
-      <c r="V417" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -40694,11 +38609,6 @@
       <c r="U418" t="b">
         <v>1</v>
       </c>
-      <c r="V418" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -40786,11 +38696,6 @@
       <c r="U419" t="b">
         <v>0</v>
       </c>
-      <c r="V419" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -40878,11 +38783,6 @@
       <c r="U420" t="b">
         <v>1</v>
       </c>
-      <c r="V420" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -40970,11 +38870,6 @@
       <c r="U421" t="b">
         <v>0</v>
       </c>
-      <c r="V421" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -41062,11 +38957,6 @@
       <c r="U422" t="b">
         <v>1</v>
       </c>
-      <c r="V422" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -41154,11 +39044,6 @@
       <c r="U423" t="b">
         <v>1</v>
       </c>
-      <c r="V423" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -41246,11 +39131,6 @@
       <c r="U424" t="b">
         <v>0</v>
       </c>
-      <c r="V424" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -41338,11 +39218,6 @@
       <c r="U425" t="b">
         <v>1</v>
       </c>
-      <c r="V425" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -41430,11 +39305,6 @@
       <c r="U426" t="b">
         <v>1</v>
       </c>
-      <c r="V426" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -41522,11 +39392,6 @@
       <c r="U427" t="b">
         <v>1</v>
       </c>
-      <c r="V427" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -41614,11 +39479,6 @@
       <c r="U428" t="b">
         <v>0</v>
       </c>
-      <c r="V428" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -41706,11 +39566,6 @@
       <c r="U429" t="b">
         <v>0</v>
       </c>
-      <c r="V429" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -41798,11 +39653,6 @@
       <c r="U430" t="b">
         <v>1</v>
       </c>
-      <c r="V430" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -41890,11 +39740,6 @@
       <c r="U431" t="b">
         <v>1</v>
       </c>
-      <c r="V431" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -41982,11 +39827,6 @@
       <c r="U432" t="b">
         <v>1</v>
       </c>
-      <c r="V432" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -42074,11 +39914,6 @@
       <c r="U433" t="b">
         <v>1</v>
       </c>
-      <c r="V433" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -42166,11 +40001,6 @@
       <c r="U434" t="b">
         <v>1</v>
       </c>
-      <c r="V434" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -42258,11 +40088,6 @@
       <c r="U435" t="b">
         <v>0</v>
       </c>
-      <c r="V435" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -42350,11 +40175,6 @@
       <c r="U436" t="b">
         <v>0</v>
       </c>
-      <c r="V436" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -42442,11 +40262,6 @@
       <c r="U437" t="b">
         <v>1</v>
       </c>
-      <c r="V437" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -42534,11 +40349,6 @@
       <c r="U438" t="b">
         <v>0</v>
       </c>
-      <c r="V438" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -42626,11 +40436,6 @@
       <c r="U439" t="b">
         <v>1</v>
       </c>
-      <c r="V439" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -42718,11 +40523,6 @@
       <c r="U440" t="b">
         <v>1</v>
       </c>
-      <c r="V440" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -42810,11 +40610,6 @@
       <c r="U441" t="b">
         <v>1</v>
       </c>
-      <c r="V441" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -42902,11 +40697,6 @@
       <c r="U442" t="b">
         <v>1</v>
       </c>
-      <c r="V442" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -42994,11 +40784,6 @@
       <c r="U443" t="b">
         <v>1</v>
       </c>
-      <c r="V443" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -43086,11 +40871,6 @@
       <c r="U444" t="b">
         <v>1</v>
       </c>
-      <c r="V444" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -43178,11 +40958,6 @@
       <c r="U445" t="b">
         <v>0</v>
       </c>
-      <c r="V445" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -43270,11 +41045,6 @@
       <c r="U446" t="b">
         <v>1</v>
       </c>
-      <c r="V446" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -43362,11 +41132,6 @@
       <c r="U447" t="b">
         <v>1</v>
       </c>
-      <c r="V447" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -43454,11 +41219,6 @@
       <c r="U448" t="b">
         <v>1</v>
       </c>
-      <c r="V448" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -43546,11 +41306,6 @@
       <c r="U449" t="b">
         <v>1</v>
       </c>
-      <c r="V449" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -43638,11 +41393,6 @@
       <c r="U450" t="b">
         <v>1</v>
       </c>
-      <c r="V450" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -43730,11 +41480,6 @@
       <c r="U451" t="b">
         <v>1</v>
       </c>
-      <c r="V451" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -43822,11 +41567,6 @@
       <c r="U452" t="b">
         <v>1</v>
       </c>
-      <c r="V452" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -43914,11 +41654,6 @@
       <c r="U453" t="b">
         <v>1</v>
       </c>
-      <c r="V453" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -44006,11 +41741,6 @@
       <c r="U454" t="b">
         <v>1</v>
       </c>
-      <c r="V454" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -44098,11 +41828,6 @@
       <c r="U455" t="b">
         <v>1</v>
       </c>
-      <c r="V455" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -44190,11 +41915,6 @@
       <c r="U456" t="b">
         <v>1</v>
       </c>
-      <c r="V456" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -44282,11 +42002,6 @@
       <c r="U457" t="b">
         <v>0</v>
       </c>
-      <c r="V457" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -44374,11 +42089,6 @@
       <c r="U458" t="b">
         <v>1</v>
       </c>
-      <c r="V458" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -44466,11 +42176,6 @@
       <c r="U459" t="b">
         <v>1</v>
       </c>
-      <c r="V459" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -44558,11 +42263,6 @@
       <c r="U460" t="b">
         <v>0</v>
       </c>
-      <c r="V460" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -44650,11 +42350,6 @@
       <c r="U461" t="b">
         <v>1</v>
       </c>
-      <c r="V461" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -44742,11 +42437,6 @@
       <c r="U462" t="b">
         <v>1</v>
       </c>
-      <c r="V462" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -44834,11 +42524,6 @@
       <c r="U463" t="b">
         <v>1</v>
       </c>
-      <c r="V463" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -44926,11 +42611,6 @@
       <c r="U464" t="b">
         <v>1</v>
       </c>
-      <c r="V464" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -45018,11 +42698,6 @@
       <c r="U465" t="b">
         <v>1</v>
       </c>
-      <c r="V465" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -45110,11 +42785,6 @@
       <c r="U466" t="b">
         <v>1</v>
       </c>
-      <c r="V466" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -45202,11 +42872,6 @@
       <c r="U467" t="b">
         <v>0</v>
       </c>
-      <c r="V467" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -45294,11 +42959,6 @@
       <c r="U468" t="b">
         <v>0</v>
       </c>
-      <c r="V468" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -45386,11 +43046,6 @@
       <c r="U469" t="b">
         <v>1</v>
       </c>
-      <c r="V469" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -45478,11 +43133,6 @@
       <c r="U470" t="b">
         <v>1</v>
       </c>
-      <c r="V470" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -45570,11 +43220,6 @@
       <c r="U471" t="b">
         <v>1</v>
       </c>
-      <c r="V471" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -45662,11 +43307,6 @@
       <c r="U472" t="b">
         <v>0</v>
       </c>
-      <c r="V472" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -45754,11 +43394,6 @@
       <c r="U473" t="b">
         <v>1</v>
       </c>
-      <c r="V473" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -45846,11 +43481,6 @@
       <c r="U474" t="b">
         <v>1</v>
       </c>
-      <c r="V474" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -45938,11 +43568,6 @@
       <c r="U475" t="b">
         <v>1</v>
       </c>
-      <c r="V475" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -46030,11 +43655,6 @@
       <c r="U476" t="b">
         <v>1</v>
       </c>
-      <c r="V476" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -46122,11 +43742,6 @@
       <c r="U477" t="b">
         <v>0</v>
       </c>
-      <c r="V477" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -46214,11 +43829,6 @@
       <c r="U478" t="b">
         <v>1</v>
       </c>
-      <c r="V478" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -46306,11 +43916,6 @@
       <c r="U479" t="b">
         <v>1</v>
       </c>
-      <c r="V479" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -46398,11 +44003,6 @@
       <c r="U480" t="b">
         <v>1</v>
       </c>
-      <c r="V480" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -46490,11 +44090,6 @@
       <c r="U481" t="b">
         <v>1</v>
       </c>
-      <c r="V481" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -46582,11 +44177,6 @@
       <c r="U482" t="b">
         <v>0</v>
       </c>
-      <c r="V482" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -46674,11 +44264,6 @@
       <c r="U483" t="b">
         <v>1</v>
       </c>
-      <c r="V483" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -46766,11 +44351,6 @@
       <c r="U484" t="b">
         <v>1</v>
       </c>
-      <c r="V484" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -46858,11 +44438,6 @@
       <c r="U485" t="b">
         <v>0</v>
       </c>
-      <c r="V485" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -46950,11 +44525,6 @@
       <c r="U486" t="b">
         <v>1</v>
       </c>
-      <c r="V486" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -47042,11 +44612,6 @@
       <c r="U487" t="b">
         <v>1</v>
       </c>
-      <c r="V487" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -47134,11 +44699,6 @@
       <c r="U488" t="b">
         <v>1</v>
       </c>
-      <c r="V488" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -47226,11 +44786,6 @@
       <c r="U489" t="b">
         <v>1</v>
       </c>
-      <c r="V489" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -47318,11 +44873,6 @@
       <c r="U490" t="b">
         <v>1</v>
       </c>
-      <c r="V490" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -47410,11 +44960,6 @@
       <c r="U491" t="b">
         <v>1</v>
       </c>
-      <c r="V491" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -47502,11 +45047,6 @@
       <c r="U492" t="b">
         <v>1</v>
       </c>
-      <c r="V492" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -47594,11 +45134,6 @@
       <c r="U493" t="b">
         <v>1</v>
       </c>
-      <c r="V493" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -47686,11 +45221,6 @@
       <c r="U494" t="b">
         <v>0</v>
       </c>
-      <c r="V494" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -47778,11 +45308,6 @@
       <c r="U495" t="b">
         <v>0</v>
       </c>
-      <c r="V495" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -47870,11 +45395,6 @@
       <c r="U496" t="b">
         <v>1</v>
       </c>
-      <c r="V496" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -47962,11 +45482,6 @@
       <c r="U497" t="b">
         <v>1</v>
       </c>
-      <c r="V497" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -48054,11 +45569,6 @@
       <c r="U498" t="b">
         <v>1</v>
       </c>
-      <c r="V498" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -48146,11 +45656,6 @@
       <c r="U499" t="b">
         <v>1</v>
       </c>
-      <c r="V499" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -48238,11 +45743,6 @@
       <c r="U500" t="b">
         <v>1</v>
       </c>
-      <c r="V500" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -48330,11 +45830,6 @@
       <c r="U501" t="b">
         <v>1</v>
       </c>
-      <c r="V501" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -48422,11 +45917,6 @@
       <c r="U502" t="b">
         <v>1</v>
       </c>
-      <c r="V502" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -48514,11 +46004,6 @@
       <c r="U503" t="b">
         <v>0</v>
       </c>
-      <c r="V503" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -48606,11 +46091,6 @@
       <c r="U504" t="b">
         <v>1</v>
       </c>
-      <c r="V504" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -48698,11 +46178,6 @@
       <c r="U505" t="b">
         <v>1</v>
       </c>
-      <c r="V505" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -48790,11 +46265,6 @@
       <c r="U506" t="b">
         <v>1</v>
       </c>
-      <c r="V506" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -48882,11 +46352,6 @@
       <c r="U507" t="b">
         <v>0</v>
       </c>
-      <c r="V507" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -48974,11 +46439,6 @@
       <c r="U508" t="b">
         <v>1</v>
       </c>
-      <c r="V508" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -49066,11 +46526,6 @@
       <c r="U509" t="b">
         <v>1</v>
       </c>
-      <c r="V509" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -49158,11 +46613,6 @@
       <c r="U510" t="b">
         <v>1</v>
       </c>
-      <c r="V510" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -49250,11 +46700,6 @@
       <c r="U511" t="b">
         <v>1</v>
       </c>
-      <c r="V511" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -49342,11 +46787,6 @@
       <c r="U512" t="b">
         <v>1</v>
       </c>
-      <c r="V512" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -49434,11 +46874,6 @@
       <c r="U513" t="b">
         <v>0</v>
       </c>
-      <c r="V513" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -49526,11 +46961,6 @@
       <c r="U514" t="b">
         <v>1</v>
       </c>
-      <c r="V514" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -49618,11 +47048,6 @@
       <c r="U515" t="b">
         <v>1</v>
       </c>
-      <c r="V515" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -49710,11 +47135,6 @@
       <c r="U516" t="b">
         <v>1</v>
       </c>
-      <c r="V516" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -49802,11 +47222,6 @@
       <c r="U517" t="b">
         <v>1</v>
       </c>
-      <c r="V517" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -49894,11 +47309,6 @@
       <c r="U518" t="b">
         <v>0</v>
       </c>
-      <c r="V518" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -49986,11 +47396,6 @@
       <c r="U519" t="b">
         <v>1</v>
       </c>
-      <c r="V519" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -50078,11 +47483,6 @@
       <c r="U520" t="b">
         <v>1</v>
       </c>
-      <c r="V520" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -50170,11 +47570,6 @@
       <c r="U521" t="b">
         <v>1</v>
       </c>
-      <c r="V521" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -50262,11 +47657,6 @@
       <c r="U522" t="b">
         <v>1</v>
       </c>
-      <c r="V522" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -50354,11 +47744,6 @@
       <c r="U523" t="b">
         <v>0</v>
       </c>
-      <c r="V523" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -50446,11 +47831,6 @@
       <c r="U524" t="b">
         <v>1</v>
       </c>
-      <c r="V524" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -50538,11 +47918,6 @@
       <c r="U525" t="b">
         <v>1</v>
       </c>
-      <c r="V525" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -50630,11 +48005,6 @@
       <c r="U526" t="b">
         <v>1</v>
       </c>
-      <c r="V526" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -50722,11 +48092,6 @@
       <c r="U527" t="b">
         <v>1</v>
       </c>
-      <c r="V527" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -50814,11 +48179,6 @@
       <c r="U528" t="b">
         <v>1</v>
       </c>
-      <c r="V528" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -50906,11 +48266,6 @@
       <c r="U529" t="b">
         <v>1</v>
       </c>
-      <c r="V529" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -50998,11 +48353,6 @@
       <c r="U530" t="b">
         <v>1</v>
       </c>
-      <c r="V530" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -51090,11 +48440,6 @@
       <c r="U531" t="b">
         <v>0</v>
       </c>
-      <c r="V531" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -51182,11 +48527,6 @@
       <c r="U532" t="b">
         <v>1</v>
       </c>
-      <c r="V532" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -51274,11 +48614,6 @@
       <c r="U533" t="b">
         <v>1</v>
       </c>
-      <c r="V533" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -51366,11 +48701,6 @@
       <c r="U534" t="b">
         <v>1</v>
       </c>
-      <c r="V534" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -51458,11 +48788,6 @@
       <c r="U535" t="b">
         <v>0</v>
       </c>
-      <c r="V535" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -51550,11 +48875,6 @@
       <c r="U536" t="b">
         <v>0</v>
       </c>
-      <c r="V536" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -51642,11 +48962,6 @@
       <c r="U537" t="b">
         <v>1</v>
       </c>
-      <c r="V537" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -51734,11 +49049,6 @@
       <c r="U538" t="b">
         <v>1</v>
       </c>
-      <c r="V538" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -51826,11 +49136,6 @@
       <c r="U539" t="b">
         <v>1</v>
       </c>
-      <c r="V539" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -51918,11 +49223,6 @@
       <c r="U540" t="b">
         <v>1</v>
       </c>
-      <c r="V540" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -52010,11 +49310,6 @@
       <c r="U541" t="b">
         <v>1</v>
       </c>
-      <c r="V541" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -52102,11 +49397,6 @@
       <c r="U542" t="b">
         <v>1</v>
       </c>
-      <c r="V542" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -52194,11 +49484,6 @@
       <c r="U543" t="b">
         <v>1</v>
       </c>
-      <c r="V543" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -52286,11 +49571,6 @@
       <c r="U544" t="b">
         <v>1</v>
       </c>
-      <c r="V544" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -52378,11 +49658,6 @@
       <c r="U545" t="b">
         <v>1</v>
       </c>
-      <c r="V545" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -52470,11 +49745,6 @@
       <c r="U546" t="b">
         <v>1</v>
       </c>
-      <c r="V546" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -52562,11 +49832,6 @@
       <c r="U547" t="b">
         <v>1</v>
       </c>
-      <c r="V547" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -52654,11 +49919,6 @@
       <c r="U548" t="b">
         <v>1</v>
       </c>
-      <c r="V548" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -52746,11 +50006,6 @@
       <c r="U549" t="b">
         <v>1</v>
       </c>
-      <c r="V549" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -52838,11 +50093,6 @@
       <c r="U550" t="b">
         <v>1</v>
       </c>
-      <c r="V550" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -52930,11 +50180,6 @@
       <c r="U551" t="b">
         <v>1</v>
       </c>
-      <c r="V551" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -53022,11 +50267,6 @@
       <c r="U552" t="b">
         <v>1</v>
       </c>
-      <c r="V552" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -53114,11 +50354,6 @@
       <c r="U553" t="b">
         <v>1</v>
       </c>
-      <c r="V553" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -53206,11 +50441,6 @@
       <c r="U554" t="b">
         <v>0</v>
       </c>
-      <c r="V554" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -53298,11 +50528,6 @@
       <c r="U555" t="b">
         <v>1</v>
       </c>
-      <c r="V555" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -53390,11 +50615,6 @@
       <c r="U556" t="b">
         <v>1</v>
       </c>
-      <c r="V556" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -53482,11 +50702,6 @@
       <c r="U557" t="b">
         <v>0</v>
       </c>
-      <c r="V557" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -53574,11 +50789,6 @@
       <c r="U558" t="b">
         <v>1</v>
       </c>
-      <c r="V558" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -53666,11 +50876,6 @@
       <c r="U559" t="b">
         <v>1</v>
       </c>
-      <c r="V559" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -53758,11 +50963,6 @@
       <c r="U560" t="b">
         <v>0</v>
       </c>
-      <c r="V560" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -53850,11 +51050,6 @@
       <c r="U561" t="b">
         <v>1</v>
       </c>
-      <c r="V561" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -53942,11 +51137,6 @@
       <c r="U562" t="b">
         <v>1</v>
       </c>
-      <c r="V562" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -54034,11 +51224,6 @@
       <c r="U563" t="b">
         <v>1</v>
       </c>
-      <c r="V563" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -54126,11 +51311,6 @@
       <c r="U564" t="b">
         <v>1</v>
       </c>
-      <c r="V564" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -54218,11 +51398,6 @@
       <c r="U565" t="b">
         <v>0</v>
       </c>
-      <c r="V565" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -54310,11 +51485,6 @@
       <c r="U566" t="b">
         <v>0</v>
       </c>
-      <c r="V566" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -54402,11 +51572,6 @@
       <c r="U567" t="b">
         <v>1</v>
       </c>
-      <c r="V567" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -54494,11 +51659,6 @@
       <c r="U568" t="b">
         <v>1</v>
       </c>
-      <c r="V568" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -54586,11 +51746,6 @@
       <c r="U569" t="b">
         <v>0</v>
       </c>
-      <c r="V569" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -54678,11 +51833,6 @@
       <c r="U570" t="b">
         <v>1</v>
       </c>
-      <c r="V570" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -54770,11 +51920,6 @@
       <c r="U571" t="b">
         <v>1</v>
       </c>
-      <c r="V571" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -54862,11 +52007,6 @@
       <c r="U572" t="b">
         <v>1</v>
       </c>
-      <c r="V572" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -54954,11 +52094,6 @@
       <c r="U573" t="b">
         <v>1</v>
       </c>
-      <c r="V573" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -55046,11 +52181,6 @@
       <c r="U574" t="b">
         <v>0</v>
       </c>
-      <c r="V574" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -55138,11 +52268,6 @@
       <c r="U575" t="b">
         <v>1</v>
       </c>
-      <c r="V575" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -55230,11 +52355,6 @@
       <c r="U576" t="b">
         <v>1</v>
       </c>
-      <c r="V576" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -55322,11 +52442,6 @@
       <c r="U577" t="b">
         <v>1</v>
       </c>
-      <c r="V577" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -55414,11 +52529,6 @@
       <c r="U578" t="b">
         <v>1</v>
       </c>
-      <c r="V578" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -55506,11 +52616,6 @@
       <c r="U579" t="b">
         <v>1</v>
       </c>
-      <c r="V579" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -55598,11 +52703,6 @@
       <c r="U580" t="b">
         <v>1</v>
       </c>
-      <c r="V580" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -55690,11 +52790,6 @@
       <c r="U581" t="b">
         <v>0</v>
       </c>
-      <c r="V581" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -55782,11 +52877,6 @@
       <c r="U582" t="b">
         <v>1</v>
       </c>
-      <c r="V582" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -55874,11 +52964,6 @@
       <c r="U583" t="b">
         <v>1</v>
       </c>
-      <c r="V583" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -55966,11 +53051,6 @@
       <c r="U584" t="b">
         <v>0</v>
       </c>
-      <c r="V584" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -56058,11 +53138,6 @@
       <c r="U585" t="b">
         <v>0</v>
       </c>
-      <c r="V585" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -56150,11 +53225,6 @@
       <c r="U586" t="b">
         <v>0</v>
       </c>
-      <c r="V586" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -56242,11 +53312,6 @@
       <c r="U587" t="b">
         <v>1</v>
       </c>
-      <c r="V587" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -56334,11 +53399,6 @@
       <c r="U588" t="b">
         <v>1</v>
       </c>
-      <c r="V588" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -56426,11 +53486,6 @@
       <c r="U589" t="b">
         <v>0</v>
       </c>
-      <c r="V589" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -56518,11 +53573,6 @@
       <c r="U590" t="b">
         <v>1</v>
       </c>
-      <c r="V590" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -56610,11 +53660,6 @@
       <c r="U591" t="b">
         <v>0</v>
       </c>
-      <c r="V591" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -56702,11 +53747,6 @@
       <c r="U592" t="b">
         <v>1</v>
       </c>
-      <c r="V592" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -56794,11 +53834,6 @@
       <c r="U593" t="b">
         <v>1</v>
       </c>
-      <c r="V593" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -56886,11 +53921,6 @@
       <c r="U594" t="b">
         <v>1</v>
       </c>
-      <c r="V594" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -56978,11 +54008,6 @@
       <c r="U595" t="b">
         <v>0</v>
       </c>
-      <c r="V595" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -57070,11 +54095,6 @@
       <c r="U596" t="b">
         <v>1</v>
       </c>
-      <c r="V596" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -57162,11 +54182,6 @@
       <c r="U597" t="b">
         <v>1</v>
       </c>
-      <c r="V597" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -57254,11 +54269,6 @@
       <c r="U598" t="b">
         <v>1</v>
       </c>
-      <c r="V598" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -57346,11 +54356,6 @@
       <c r="U599" t="b">
         <v>0</v>
       </c>
-      <c r="V599" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -57438,11 +54443,6 @@
       <c r="U600" t="b">
         <v>1</v>
       </c>
-      <c r="V600" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -57530,11 +54530,6 @@
       <c r="U601" t="b">
         <v>1</v>
       </c>
-      <c r="V601" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -57622,11 +54617,6 @@
       <c r="U602" t="b">
         <v>0</v>
       </c>
-      <c r="V602" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -57714,11 +54704,6 @@
       <c r="U603" t="b">
         <v>1</v>
       </c>
-      <c r="V603" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -57806,11 +54791,6 @@
       <c r="U604" t="b">
         <v>1</v>
       </c>
-      <c r="V604" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -57898,11 +54878,6 @@
       <c r="U605" t="b">
         <v>0</v>
       </c>
-      <c r="V605" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -57990,11 +54965,6 @@
       <c r="U606" t="b">
         <v>1</v>
       </c>
-      <c r="V606" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -58082,11 +55052,6 @@
       <c r="U607" t="b">
         <v>1</v>
       </c>
-      <c r="V607" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -58174,11 +55139,6 @@
       <c r="U608" t="b">
         <v>1</v>
       </c>
-      <c r="V608" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -58266,11 +55226,6 @@
       <c r="U609" t="b">
         <v>1</v>
       </c>
-      <c r="V609" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -58358,11 +55313,6 @@
       <c r="U610" t="b">
         <v>1</v>
       </c>
-      <c r="V610" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -58450,11 +55400,6 @@
       <c r="U611" t="b">
         <v>1</v>
       </c>
-      <c r="V611" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -58542,11 +55487,6 @@
       <c r="U612" t="b">
         <v>1</v>
       </c>
-      <c r="V612" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -58634,11 +55574,6 @@
       <c r="U613" t="b">
         <v>0</v>
       </c>
-      <c r="V613" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -58726,11 +55661,6 @@
       <c r="U614" t="b">
         <v>0</v>
       </c>
-      <c r="V614" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -58818,11 +55748,6 @@
       <c r="U615" t="b">
         <v>1</v>
       </c>
-      <c r="V615" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -58910,11 +55835,6 @@
       <c r="U616" t="b">
         <v>1</v>
       </c>
-      <c r="V616" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -59002,11 +55922,6 @@
       <c r="U617" t="b">
         <v>1</v>
       </c>
-      <c r="V617" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -59094,11 +56009,6 @@
       <c r="U618" t="b">
         <v>1</v>
       </c>
-      <c r="V618" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -59186,11 +56096,6 @@
       <c r="U619" t="b">
         <v>0</v>
       </c>
-      <c r="V619" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -59278,11 +56183,6 @@
       <c r="U620" t="b">
         <v>0</v>
       </c>
-      <c r="V620" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -59370,11 +56270,6 @@
       <c r="U621" t="b">
         <v>0</v>
       </c>
-      <c r="V621" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -59462,11 +56357,6 @@
       <c r="U622" t="b">
         <v>1</v>
       </c>
-      <c r="V622" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -59554,11 +56444,6 @@
       <c r="U623" t="b">
         <v>1</v>
       </c>
-      <c r="V623" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -59646,11 +56531,6 @@
       <c r="U624" t="b">
         <v>1</v>
       </c>
-      <c r="V624" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -59738,11 +56618,6 @@
       <c r="U625" t="b">
         <v>1</v>
       </c>
-      <c r="V625" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -59830,11 +56705,6 @@
       <c r="U626" t="b">
         <v>1</v>
       </c>
-      <c r="V626" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -59922,11 +56792,6 @@
       <c r="U627" t="b">
         <v>0</v>
       </c>
-      <c r="V627" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -60014,11 +56879,6 @@
       <c r="U628" t="b">
         <v>1</v>
       </c>
-      <c r="V628" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -60106,11 +56966,6 @@
       <c r="U629" t="b">
         <v>1</v>
       </c>
-      <c r="V629" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -60198,11 +57053,6 @@
       <c r="U630" t="b">
         <v>1</v>
       </c>
-      <c r="V630" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -60290,11 +57140,6 @@
       <c r="U631" t="b">
         <v>1</v>
       </c>
-      <c r="V631" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -60382,11 +57227,6 @@
       <c r="U632" t="b">
         <v>1</v>
       </c>
-      <c r="V632" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -60474,11 +57314,6 @@
       <c r="U633" t="b">
         <v>1</v>
       </c>
-      <c r="V633" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -60566,11 +57401,6 @@
       <c r="U634" t="b">
         <v>1</v>
       </c>
-      <c r="V634" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -60658,11 +57488,6 @@
       <c r="U635" t="b">
         <v>1</v>
       </c>
-      <c r="V635" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -60750,11 +57575,6 @@
       <c r="U636" t="b">
         <v>1</v>
       </c>
-      <c r="V636" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -60842,11 +57662,6 @@
       <c r="U637" t="b">
         <v>1</v>
       </c>
-      <c r="V637" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -60934,11 +57749,6 @@
       <c r="U638" t="b">
         <v>1</v>
       </c>
-      <c r="V638" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -61026,11 +57836,6 @@
       <c r="U639" t="b">
         <v>1</v>
       </c>
-      <c r="V639" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
-      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -61118,11 +57923,6 @@
       <c r="U640" t="b">
         <v>1</v>
       </c>
-      <c r="V640" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -61209,11 +58009,6 @@
       </c>
       <c r="U641" t="b">
         <v>0</v>
-      </c>
-      <c r="V641" t="inlineStr">
-        <is>
-          <t>pre</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/data/raw/procurement_data.xlsx
+++ b/data/raw/procurement_data.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,32 +431,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>supplier_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>product_description</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
@@ -2225,107 +2237,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>po_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>supplier_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>item_description</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>unit_price_usd</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>total_value_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pr_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>po_date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>delivery_date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>invoice_date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>payment_date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>pr_to_po_days</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>po_to_delivery_days</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>delivery_to_invoice_days</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>invoice_to_payment_days</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>total_cycle_days</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>on_time_delivery</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>three_way_match_pass</t>
         </is>
@@ -58026,132 +58038,132 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>supplier_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>product_description</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>total_spend_usd</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>num_pos</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_po_value_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_lead_time_days</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_cycle_time_days</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>on_time_delivery_pct</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>three_way_match_pct</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>defect_rate_pct</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>complaint_count_annual</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rfx_response_rate_pct</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>avg_response_time_days</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>single_source_risk</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>quality_score</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>delivery_score</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>service_score</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>process_score</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>risk_score</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>composite_score</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>calculated_tier</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>tier_mismatch</t>
         </is>
@@ -58225,22 +58237,22 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>91.01000000000001</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>75.51000000000001</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>93.61</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>84.62</v>
       </c>
       <c r="W2" t="n">
-        <v>41.31</v>
+        <v>100</v>
       </c>
       <c r="X2" t="n">
-        <v>78.79000000000001</v>
+        <v>90.17</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -58319,30 +58331,30 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>87.63</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>78.43000000000001</v>
+        <v>88.48</v>
       </c>
       <c r="U3" t="n">
-        <v>97.55</v>
+        <v>94.16</v>
       </c>
       <c r="V3" t="n">
         <v>78.56999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>18.74</v>
+        <v>97</v>
       </c>
       <c r="X3" t="n">
-        <v>74.67</v>
+        <v>89.05</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -58413,22 +58425,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>97.70999999999999</v>
+        <v>96.95</v>
       </c>
       <c r="T4" t="n">
-        <v>70.44</v>
+        <v>82.44</v>
       </c>
       <c r="U4" t="n">
-        <v>88.56</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>67.73999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>47.51</v>
+        <v>100</v>
       </c>
       <c r="X4" t="n">
-        <v>76</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -58507,22 +58519,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>84.08</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>52.49</v>
+        <v>75.8</v>
       </c>
       <c r="U5" t="n">
-        <v>98.59</v>
+        <v>95.17</v>
       </c>
       <c r="V5" t="n">
         <v>88.45999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>72.84999999999999</v>
+        <v>54</v>
       </c>
       <c r="X5" t="n">
-        <v>77.55</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -58601,22 +58613,22 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>76.86</v>
+        <v>82.3</v>
       </c>
       <c r="T6" t="n">
-        <v>49.67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>95.06999999999999</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>69.23</v>
       </c>
       <c r="W6" t="n">
-        <v>30.1</v>
+        <v>51</v>
       </c>
       <c r="X6" t="n">
-        <v>64.25</v>
+        <v>74</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -58695,30 +58707,30 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>84.2</v>
+        <v>88.05</v>
       </c>
       <c r="T7" t="n">
-        <v>56.91</v>
+        <v>79.11</v>
       </c>
       <c r="U7" t="n">
-        <v>93.56</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>73.33</v>
       </c>
       <c r="W7" t="n">
-        <v>33.6</v>
+        <v>57</v>
       </c>
       <c r="X7" t="n">
-        <v>69.02</v>
+        <v>78.63</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -58789,30 +58801,30 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>38.24</v>
+        <v>56.15</v>
       </c>
       <c r="T8" t="n">
-        <v>73.44</v>
+        <v>84.28</v>
       </c>
       <c r="U8" t="n">
-        <v>82.27</v>
+        <v>80.92</v>
       </c>
       <c r="V8" t="n">
         <v>100</v>
       </c>
       <c r="W8" t="n">
-        <v>58.81</v>
+        <v>79</v>
       </c>
       <c r="X8" t="n">
-        <v>69.08</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -58883,30 +58895,30 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>72.23</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>53.7</v>
+        <v>77.23</v>
       </c>
       <c r="U9" t="n">
-        <v>75.56999999999999</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>91.67</v>
       </c>
       <c r="W9" t="n">
-        <v>56.26</v>
+        <v>54</v>
       </c>
       <c r="X9" t="n">
-        <v>69.59</v>
+        <v>76.61</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -58977,30 +58989,30 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>73.7</v>
+        <v>81</v>
       </c>
       <c r="T10" t="n">
-        <v>79.45999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="U10" t="n">
-        <v>89.88</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>63.64</v>
       </c>
       <c r="W10" t="n">
-        <v>48.16</v>
+        <v>94</v>
       </c>
       <c r="X10" t="n">
-        <v>71.72</v>
+        <v>82.61</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -59071,30 +59083,30 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>91.47</v>
+        <v>92.5</v>
       </c>
       <c r="T11" t="n">
-        <v>53.97</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>95.41</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>73.91</v>
       </c>
       <c r="W11" t="n">
-        <v>44.97</v>
+        <v>57</v>
       </c>
       <c r="X11" t="n">
-        <v>72.2</v>
+        <v>79.69</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -59165,22 +59177,22 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>67.43000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>82.3</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>93.48999999999999</v>
+        <v>90.41</v>
       </c>
       <c r="V12" t="n">
         <v>75</v>
       </c>
       <c r="W12" t="n">
-        <v>71.25</v>
+        <v>88</v>
       </c>
       <c r="X12" t="n">
-        <v>77.14</v>
+        <v>83.78</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -59259,22 +59271,22 @@
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>62.48</v>
+        <v>73.5</v>
       </c>
       <c r="T13" t="n">
-        <v>49.16</v>
+        <v>74.44</v>
       </c>
       <c r="U13" t="n">
-        <v>84.67</v>
+        <v>80.64</v>
       </c>
       <c r="V13" t="n">
         <v>77.78</v>
       </c>
       <c r="W13" t="n">
-        <v>81.59999999999999</v>
+        <v>21</v>
       </c>
       <c r="X13" t="n">
-        <v>68.41</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -59353,26 +59365,26 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>60.4</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>83.02</v>
+        <v>92.5</v>
       </c>
       <c r="U14" t="n">
-        <v>65.23</v>
+        <v>62.35</v>
       </c>
       <c r="V14" t="n">
         <v>66.67</v>
       </c>
       <c r="W14" t="n">
-        <v>56.88</v>
+        <v>88</v>
       </c>
       <c r="X14" t="n">
-        <v>67.51000000000001</v>
+        <v>76.91</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z14" t="b">
@@ -59447,22 +59459,22 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>89.18000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>83.15000000000001</v>
+        <v>92.56</v>
       </c>
       <c r="U15" t="n">
-        <v>96.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="V15" t="n">
         <v>55.17</v>
       </c>
       <c r="W15" t="n">
-        <v>67.05</v>
+        <v>67</v>
       </c>
       <c r="X15" t="n">
-        <v>78.70999999999999</v>
+        <v>81.05</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -59541,22 +59553,22 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>95.18000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>56.16</v>
+        <v>78.77</v>
       </c>
       <c r="U16" t="n">
-        <v>93.78</v>
+        <v>91.38</v>
       </c>
       <c r="V16" t="n">
         <v>73.33</v>
       </c>
       <c r="W16" t="n">
-        <v>67.29000000000001</v>
+        <v>76</v>
       </c>
       <c r="X16" t="n">
-        <v>76.66</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -59635,22 +59647,22 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>81.3</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>63.07</v>
+        <v>75.72</v>
       </c>
       <c r="U17" t="n">
-        <v>60.75</v>
+        <v>61.82</v>
       </c>
       <c r="V17" t="n">
         <v>42.86</v>
       </c>
       <c r="W17" t="n">
-        <v>34.47</v>
+        <v>94</v>
       </c>
       <c r="X17" t="n">
-        <v>58.95</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -59729,22 +59741,22 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>81.20999999999999</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>76.41</v>
+        <v>86.09</v>
       </c>
       <c r="U18" t="n">
-        <v>98.5</v>
+        <v>95.59</v>
       </c>
       <c r="V18" t="n">
         <v>87.5</v>
       </c>
       <c r="W18" t="n">
-        <v>50.48</v>
+        <v>70</v>
       </c>
       <c r="X18" t="n">
-        <v>79.25</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -59823,22 +59835,22 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>74.19</v>
+        <v>81.3</v>
       </c>
       <c r="T19" t="n">
-        <v>67.87</v>
+        <v>80.22</v>
       </c>
       <c r="U19" t="n">
-        <v>83.36</v>
+        <v>81.14</v>
       </c>
       <c r="V19" t="n">
         <v>53.33</v>
       </c>
       <c r="W19" t="n">
-        <v>32.57</v>
+        <v>64</v>
       </c>
       <c r="X19" t="n">
-        <v>63.57</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -59917,30 +59929,30 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>62.77</v>
+        <v>73.05</v>
       </c>
       <c r="T20" t="n">
-        <v>81.13</v>
+        <v>91.67</v>
       </c>
       <c r="U20" t="n">
-        <v>81.61</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>50</v>
       </c>
       <c r="W20" t="n">
-        <v>71.72</v>
+        <v>88</v>
       </c>
       <c r="X20" t="n">
-        <v>68.97</v>
+        <v>76.63</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -60011,22 +60023,22 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>63.33</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>43.33</v>
+        <v>68.53</v>
       </c>
       <c r="U21" t="n">
-        <v>82.78</v>
+        <v>83.08</v>
       </c>
       <c r="V21" t="n">
         <v>84.62</v>
       </c>
       <c r="W21" t="n">
-        <v>64.08</v>
+        <v>54</v>
       </c>
       <c r="X21" t="n">
-        <v>65.62</v>
+        <v>73.28</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -60105,30 +60117,30 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>60.92</v>
+        <v>72.55</v>
       </c>
       <c r="T22" t="n">
-        <v>61.79</v>
+        <v>83.12</v>
       </c>
       <c r="U22" t="n">
-        <v>74.5</v>
+        <v>75.02</v>
       </c>
       <c r="V22" t="n">
         <v>87.5</v>
       </c>
       <c r="W22" t="n">
-        <v>64.65000000000001</v>
+        <v>51</v>
       </c>
       <c r="X22" t="n">
-        <v>69.05</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -60199,22 +60211,22 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>65.62</v>
+        <v>76.05</v>
       </c>
       <c r="T23" t="n">
-        <v>59.43</v>
+        <v>82.08</v>
       </c>
       <c r="U23" t="n">
-        <v>62.68</v>
+        <v>61.62</v>
       </c>
       <c r="V23" t="n">
         <v>50</v>
       </c>
       <c r="W23" t="n">
-        <v>52.73</v>
+        <v>54</v>
       </c>
       <c r="X23" t="n">
-        <v>58.57</v>
+        <v>66.88</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -60293,22 +60305,22 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>90.36</v>
+        <v>92.45</v>
       </c>
       <c r="T24" t="n">
-        <v>72.38</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>93.23</v>
+        <v>89.63</v>
       </c>
       <c r="V24" t="n">
         <v>77.78</v>
       </c>
       <c r="W24" t="n">
-        <v>65.06</v>
+        <v>100</v>
       </c>
       <c r="X24" t="n">
-        <v>79.98</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -60387,22 +60399,22 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>74.31999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="T25" t="n">
-        <v>67.48</v>
+        <v>79.19</v>
       </c>
       <c r="U25" t="n">
-        <v>94.84</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>96.15000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>48.76</v>
+        <v>91</v>
       </c>
       <c r="X25" t="n">
-        <v>76.22</v>
+        <v>86.64</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -60481,30 +60493,30 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>92.86</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>73.89</v>
+        <v>84.87</v>
       </c>
       <c r="U26" t="n">
-        <v>89.23</v>
+        <v>85.33</v>
       </c>
       <c r="V26" t="n">
         <v>54.84</v>
       </c>
       <c r="W26" t="n">
-        <v>37.34</v>
+        <v>97</v>
       </c>
       <c r="X26" t="n">
-        <v>71.64</v>
+        <v>82.87</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -60575,30 +60587,30 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>64.84999999999999</v>
+        <v>74.95</v>
       </c>
       <c r="T27" t="n">
-        <v>69.65000000000001</v>
+        <v>81.94</v>
       </c>
       <c r="U27" t="n">
-        <v>68.48</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>100</v>
       </c>
       <c r="W27" t="n">
-        <v>46.27</v>
+        <v>91</v>
       </c>
       <c r="X27" t="n">
-        <v>70.84</v>
+        <v>83.38</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -60669,30 +60681,30 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>53.75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>82.40000000000001</v>
+        <v>92.22</v>
       </c>
       <c r="U28" t="n">
-        <v>80.98</v>
+        <v>79.84</v>
       </c>
       <c r="V28" t="n">
         <v>66.67</v>
       </c>
       <c r="W28" t="n">
-        <v>68.18000000000001</v>
+        <v>85</v>
       </c>
       <c r="X28" t="n">
-        <v>69.75</v>
+        <v>77.84</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -60763,22 +60775,22 @@
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>58.39</v>
+        <v>71</v>
       </c>
       <c r="T29" t="n">
-        <v>82.64</v>
+        <v>92.33</v>
       </c>
       <c r="U29" t="n">
-        <v>20.69</v>
+        <v>19.9</v>
       </c>
       <c r="V29" t="n">
         <v>100</v>
       </c>
       <c r="W29" t="n">
-        <v>59.31</v>
+        <v>61</v>
       </c>
       <c r="X29" t="n">
-        <v>67.26000000000001</v>
+        <v>72.97</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -60857,22 +60869,22 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>35.71</v>
+        <v>57.75</v>
       </c>
       <c r="T30" t="n">
-        <v>49.53</v>
+        <v>63.75</v>
       </c>
       <c r="U30" t="n">
-        <v>45.15</v>
+        <v>49.22</v>
       </c>
       <c r="V30" t="n">
         <v>100</v>
       </c>
       <c r="W30" t="n">
-        <v>57.33</v>
+        <v>94</v>
       </c>
       <c r="X30" t="n">
-        <v>56.68</v>
+        <v>71.86</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -60951,30 +60963,30 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>93.70999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="T31" t="n">
-        <v>44.8</v>
+        <v>69.28</v>
       </c>
       <c r="U31" t="n">
-        <v>95.03</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="V31" t="n">
         <v>81.81999999999999</v>
       </c>
       <c r="W31" t="n">
-        <v>63.49</v>
+        <v>60</v>
       </c>
       <c r="X31" t="n">
-        <v>74.77</v>
+        <v>80.03</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -61045,22 +61057,22 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>83.95</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="T32" t="n">
-        <v>55.77</v>
+        <v>80.47</v>
       </c>
       <c r="U32" t="n">
-        <v>81.22</v>
+        <v>78.97</v>
       </c>
       <c r="V32" t="n">
         <v>77.78</v>
       </c>
       <c r="W32" t="n">
-        <v>90.34999999999999</v>
+        <v>73</v>
       </c>
       <c r="X32" t="n">
-        <v>76.22</v>
+        <v>80.44</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -61139,22 +61151,22 @@
         <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>53.61</v>
+        <v>68.7</v>
       </c>
       <c r="T33" t="n">
-        <v>61.45</v>
+        <v>82.98</v>
       </c>
       <c r="U33" t="n">
-        <v>74.92</v>
+        <v>75.27</v>
       </c>
       <c r="V33" t="n">
         <v>57.14</v>
       </c>
       <c r="W33" t="n">
-        <v>56.77</v>
+        <v>40</v>
       </c>
       <c r="X33" t="n">
-        <v>59.95</v>
+        <v>66.64</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -61233,30 +61245,30 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>34.09</v>
+        <v>55.5</v>
       </c>
       <c r="T34" t="n">
-        <v>45.19</v>
+        <v>67.42</v>
       </c>
       <c r="U34" t="n">
-        <v>74.73</v>
+        <v>75.8</v>
       </c>
       <c r="V34" t="n">
         <v>70</v>
       </c>
       <c r="W34" t="n">
-        <v>61.66</v>
+        <v>48</v>
       </c>
       <c r="X34" t="n">
-        <v>54.28</v>
+        <v>63.3</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -61327,22 +61339,22 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>47.86</v>
+        <v>63.3</v>
       </c>
       <c r="T35" t="n">
-        <v>48.1</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="U35" t="n">
-        <v>70.73999999999999</v>
+        <v>70.89</v>
       </c>
       <c r="V35" t="n">
         <v>87.5</v>
       </c>
       <c r="W35" t="n">
-        <v>59.27</v>
+        <v>45</v>
       </c>
       <c r="X35" t="n">
-        <v>60.99</v>
+        <v>68.23</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -61421,22 +61433,22 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>16.49</v>
+        <v>44.1</v>
       </c>
       <c r="T36" t="n">
-        <v>80.19</v>
+        <v>91.25</v>
       </c>
       <c r="U36" t="n">
-        <v>79.54000000000001</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="V36" t="n">
         <v>50</v>
       </c>
       <c r="W36" t="n">
-        <v>70.05</v>
+        <v>85</v>
       </c>
       <c r="X36" t="n">
-        <v>56.61</v>
+        <v>68.13</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -61515,22 +61527,22 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>76.86</v>
+        <v>82.3</v>
       </c>
       <c r="T37" t="n">
-        <v>48.81</v>
+        <v>73.67</v>
       </c>
       <c r="U37" t="n">
-        <v>57.37</v>
+        <v>56.33</v>
       </c>
       <c r="V37" t="n">
         <v>86.67</v>
       </c>
       <c r="W37" t="n">
-        <v>88.16</v>
+        <v>67</v>
       </c>
       <c r="X37" t="n">
-        <v>70.58</v>
+        <v>74.83</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -61609,22 +61621,22 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>53.5</v>
+        <v>66.75</v>
       </c>
       <c r="T38" t="n">
-        <v>50</v>
+        <v>77.92</v>
       </c>
       <c r="U38" t="n">
-        <v>62.71</v>
+        <v>64.98</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>71.93000000000001</v>
+        <v>45</v>
       </c>
       <c r="X38" t="n">
-        <v>46.07</v>
+        <v>52.66</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -61703,30 +61715,30 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>83.51000000000001</v>
+        <v>87</v>
       </c>
       <c r="T39" t="n">
-        <v>59.04</v>
+        <v>81.91</v>
       </c>
       <c r="U39" t="n">
-        <v>73.63</v>
+        <v>73.23</v>
       </c>
       <c r="V39" t="n">
         <v>85.70999999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>49.83</v>
+        <v>54</v>
       </c>
       <c r="X39" t="n">
-        <v>71.3</v>
+        <v>78.45</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -61797,22 +61809,22 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>44.43</v>
+        <v>61.2</v>
       </c>
       <c r="T40" t="n">
-        <v>62.26</v>
+        <v>83.33</v>
       </c>
       <c r="U40" t="n">
-        <v>24.28</v>
+        <v>28.96</v>
       </c>
       <c r="V40" t="n">
         <v>100</v>
       </c>
       <c r="W40" t="n">
-        <v>59.14</v>
+        <v>61</v>
       </c>
       <c r="X40" t="n">
-        <v>59.19</v>
+        <v>69.63</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -61891,22 +61903,22 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>77.70999999999999</v>
+        <v>83.45</v>
       </c>
       <c r="T41" t="n">
-        <v>31.4</v>
+        <v>57.74</v>
       </c>
       <c r="U41" t="n">
-        <v>87.38</v>
+        <v>85.31</v>
       </c>
       <c r="V41" t="n">
         <v>85.70999999999999</v>
       </c>
       <c r="W41" t="n">
-        <v>76.68000000000001</v>
+        <v>54</v>
       </c>
       <c r="X41" t="n">
-        <v>69.03</v>
+        <v>73.34</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -61985,22 +61997,22 @@
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>69.86</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="T42" t="n">
-        <v>46.83</v>
+        <v>71.44</v>
       </c>
       <c r="U42" t="n">
-        <v>83.06999999999999</v>
+        <v>83</v>
       </c>
       <c r="V42" t="n">
         <v>90.91</v>
       </c>
       <c r="W42" t="n">
-        <v>78.33</v>
+        <v>24</v>
       </c>
       <c r="X42" t="n">
-        <v>71.56</v>
+        <v>71.75</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -62079,26 +62091,26 @@
         <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>49.12</v>
+        <v>64.7</v>
       </c>
       <c r="T43" t="n">
-        <v>77.36</v>
+        <v>90</v>
       </c>
       <c r="U43" t="n">
-        <v>54.69</v>
+        <v>54.97</v>
       </c>
       <c r="V43" t="n">
         <v>100</v>
       </c>
       <c r="W43" t="n">
-        <v>65.77</v>
+        <v>58</v>
       </c>
       <c r="X43" t="n">
-        <v>69.69</v>
+        <v>75.62</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z43" t="b">
@@ -62173,30 +62185,30 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>93.38</v>
+        <v>94.3</v>
       </c>
       <c r="T44" t="n">
-        <v>53.38</v>
+        <v>75.81</v>
       </c>
       <c r="U44" t="n">
-        <v>89.2</v>
+        <v>87.3</v>
       </c>
       <c r="V44" t="n">
         <v>80.65000000000001</v>
       </c>
       <c r="W44" t="n">
-        <v>45.76</v>
+        <v>60</v>
       </c>
       <c r="X44" t="n">
-        <v>73.06</v>
+        <v>80.75</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -62267,22 +62279,22 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>81.26000000000001</v>
+        <v>86.25</v>
       </c>
       <c r="T45" t="n">
-        <v>56.76</v>
+        <v>76.25</v>
       </c>
       <c r="U45" t="n">
-        <v>86.20999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="V45" t="n">
         <v>100</v>
       </c>
       <c r="W45" t="n">
-        <v>65.98</v>
+        <v>57</v>
       </c>
       <c r="X45" t="n">
-        <v>77.33</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -62361,22 +62373,22 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>87.95999999999999</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="T46" t="n">
-        <v>42.45</v>
+        <v>65.28</v>
       </c>
       <c r="U46" t="n">
-        <v>92.78</v>
+        <v>90.8</v>
       </c>
       <c r="V46" t="n">
         <v>66.67</v>
       </c>
       <c r="W46" t="n">
-        <v>63.84</v>
+        <v>57</v>
       </c>
       <c r="X46" t="n">
-        <v>69.43000000000001</v>
+        <v>74.41</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -62455,30 +62467,30 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>64.76000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="T47" t="n">
-        <v>76.16</v>
+        <v>87.61</v>
       </c>
       <c r="U47" t="n">
-        <v>78.16</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="V47" t="n">
         <v>93.33</v>
       </c>
       <c r="W47" t="n">
-        <v>56.82</v>
+        <v>91</v>
       </c>
       <c r="X47" t="n">
-        <v>74.14</v>
+        <v>84.72</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -62549,22 +62561,22 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>69.01000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="T48" t="n">
         <v>50</v>
       </c>
       <c r="U48" t="n">
-        <v>61.22</v>
+        <v>55.32</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>68.69</v>
+        <v>91</v>
       </c>
       <c r="X48" t="n">
-        <v>49.24</v>
+        <v>53.82</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -62643,26 +62655,26 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>52.56</v>
+        <v>66.8</v>
       </c>
       <c r="T49" t="n">
-        <v>79.72</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="U49" t="n">
-        <v>77.41</v>
+        <v>74.78</v>
       </c>
       <c r="V49" t="n">
         <v>100</v>
       </c>
       <c r="W49" t="n">
-        <v>59.99</v>
+        <v>88</v>
       </c>
       <c r="X49" t="n">
-        <v>73.68000000000001</v>
+        <v>83.88</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z49" t="b">
@@ -62737,30 +62749,30 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>25.53</v>
+        <v>49</v>
       </c>
       <c r="T50" t="n">
-        <v>81.13</v>
+        <v>91.67</v>
       </c>
       <c r="U50" t="n">
-        <v>69</v>
+        <v>70.58</v>
       </c>
       <c r="V50" t="n">
         <v>33.33</v>
       </c>
       <c r="W50" t="n">
-        <v>71.19</v>
+        <v>82</v>
       </c>
       <c r="X50" t="n">
-        <v>54.36</v>
+        <v>64.72</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -62831,26 +62843,26 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>46.42</v>
+        <v>64.3</v>
       </c>
       <c r="T51" t="n">
-        <v>84.58</v>
+        <v>93.19</v>
       </c>
       <c r="U51" t="n">
-        <v>51.7</v>
+        <v>53.09</v>
       </c>
       <c r="V51" t="n">
         <v>83.33</v>
       </c>
       <c r="W51" t="n">
-        <v>51.16</v>
+        <v>94</v>
       </c>
       <c r="X51" t="n">
-        <v>64.84</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z51" t="b">
@@ -62925,22 +62937,22 @@
         <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>70.06999999999999</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>82.64</v>
+        <v>92.33</v>
       </c>
       <c r="U52" t="n">
-        <v>75.37</v>
+        <v>77.09</v>
       </c>
       <c r="V52" t="n">
         <v>100</v>
       </c>
       <c r="W52" t="n">
-        <v>58.15</v>
+        <v>61</v>
       </c>
       <c r="X52" t="n">
-        <v>78.20999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -63019,22 +63031,22 @@
         <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>22.41</v>
+        <v>48.35</v>
       </c>
       <c r="T53" t="n">
-        <v>66.81999999999999</v>
+        <v>80.69</v>
       </c>
       <c r="U53" t="n">
-        <v>45.14</v>
+        <v>51.87</v>
       </c>
       <c r="V53" t="n">
         <v>100</v>
       </c>
       <c r="W53" t="n">
-        <v>67.3</v>
+        <v>58</v>
       </c>
       <c r="X53" t="n">
-        <v>59.17</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -63113,26 +63125,26 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>64.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="T54" t="n">
-        <v>84.91</v>
+        <v>93.33</v>
       </c>
       <c r="U54" t="n">
-        <v>89.40000000000001</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="V54" t="n">
         <v>100</v>
       </c>
       <c r="W54" t="n">
-        <v>26.75</v>
+        <v>91</v>
       </c>
       <c r="X54" t="n">
-        <v>74.8</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="Z54" t="b">
@@ -63207,30 +63219,30 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>60.22</v>
+        <v>72.75</v>
       </c>
       <c r="T55" t="n">
-        <v>84.91</v>
+        <v>93.33</v>
       </c>
       <c r="U55" t="n">
-        <v>61.82</v>
+        <v>58.12</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>44.21</v>
+        <v>94</v>
       </c>
       <c r="X55" t="n">
-        <v>52.19</v>
+        <v>64.34</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="Z55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -63301,22 +63313,22 @@
         <v>1</v>
       </c>
       <c r="S56" t="n">
-        <v>42.08</v>
+        <v>58.5</v>
       </c>
       <c r="T56" t="n">
-        <v>52.36</v>
+        <v>65</v>
       </c>
       <c r="U56" t="n">
-        <v>71.77</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="V56" t="n">
         <v>100</v>
       </c>
       <c r="W56" t="n">
-        <v>50.49</v>
+        <v>49</v>
       </c>
       <c r="X56" t="n">
-        <v>61.95</v>
+        <v>68.94</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>

--- a/data/raw/procurement_data.xlsx
+++ b/data/raw/procurement_data.xlsx
@@ -2233,7 +2233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U641"/>
+  <dimension ref="A1:U648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58021,6 +58021,615 @@
       </c>
       <c r="U641" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>PO-2024-00901</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>S101</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>PT Gunung Raja Paksi</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Local Steel</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Deformed rebar (BjTS 420)</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>tonne</t>
+        </is>
+      </c>
+      <c r="G642" t="n">
+        <v>120</v>
+      </c>
+      <c r="H642" t="n">
+        <v>850</v>
+      </c>
+      <c r="I642" t="n">
+        <v>102000</v>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="O642" t="n">
+        <v>5</v>
+      </c>
+      <c r="P642" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q642" t="n">
+        <v>4</v>
+      </c>
+      <c r="R642" t="n">
+        <v>18</v>
+      </c>
+      <c r="S642" t="n">
+        <v>37</v>
+      </c>
+      <c r="T642" t="b">
+        <v>1</v>
+      </c>
+      <c r="U642" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>PO-2024-00902</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>S101</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>PT Gunung Raja Paksi</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Local Steel</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Structural H-beam steel</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>tonne</t>
+        </is>
+      </c>
+      <c r="G643" t="n">
+        <v>80</v>
+      </c>
+      <c r="H643" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I643" t="n">
+        <v>88000</v>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="O643" t="n">
+        <v>6</v>
+      </c>
+      <c r="P643" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q643" t="n">
+        <v>5</v>
+      </c>
+      <c r="R643" t="n">
+        <v>20</v>
+      </c>
+      <c r="S643" t="n">
+        <v>43</v>
+      </c>
+      <c r="T643" t="b">
+        <v>1</v>
+      </c>
+      <c r="U643" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>PO-2025-00903</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>S101</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>PT Gunung Raja Paksi</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Local Steel</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Hot-rolled steel plate</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>tonne</t>
+        </is>
+      </c>
+      <c r="G644" t="n">
+        <v>150</v>
+      </c>
+      <c r="H644" t="n">
+        <v>950</v>
+      </c>
+      <c r="I644" t="n">
+        <v>142500</v>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="O644" t="n">
+        <v>7</v>
+      </c>
+      <c r="P644" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q644" t="n">
+        <v>6</v>
+      </c>
+      <c r="R644" t="n">
+        <v>15</v>
+      </c>
+      <c r="S644" t="n">
+        <v>48</v>
+      </c>
+      <c r="T644" t="b">
+        <v>0</v>
+      </c>
+      <c r="U644" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>PO-2025-00904</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>S101</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>PT Gunung Raja Paksi</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Local Steel</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Cold-rolled steel coil</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>tonne</t>
+        </is>
+      </c>
+      <c r="G645" t="n">
+        <v>200</v>
+      </c>
+      <c r="H645" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I645" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="O645" t="n">
+        <v>4</v>
+      </c>
+      <c r="P645" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q645" t="n">
+        <v>3</v>
+      </c>
+      <c r="R645" t="n">
+        <v>22</v>
+      </c>
+      <c r="S645" t="n">
+        <v>42</v>
+      </c>
+      <c r="T645" t="b">
+        <v>1</v>
+      </c>
+      <c r="U645" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>PO-2025-00905</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>S101</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>PT Gunung Raja Paksi</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Local Steel</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Steel angle bar</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>tonne</t>
+        </is>
+      </c>
+      <c r="G646" t="n">
+        <v>90</v>
+      </c>
+      <c r="H646" t="n">
+        <v>900</v>
+      </c>
+      <c r="I646" t="n">
+        <v>81000</v>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="O646" t="n">
+        <v>8</v>
+      </c>
+      <c r="P646" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q646" t="n">
+        <v>5</v>
+      </c>
+      <c r="R646" t="n">
+        <v>19</v>
+      </c>
+      <c r="S646" t="n">
+        <v>46</v>
+      </c>
+      <c r="T646" t="b">
+        <v>1</v>
+      </c>
+      <c r="U646" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>PO-2026-00906</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>S101</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>PT Gunung Raja Paksi</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Local Steel</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Galvanized steel sheet</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>tonne</t>
+        </is>
+      </c>
+      <c r="G647" t="n">
+        <v>110</v>
+      </c>
+      <c r="H647" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I647" t="n">
+        <v>132000</v>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="O647" t="n">
+        <v>5</v>
+      </c>
+      <c r="P647" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q647" t="n">
+        <v>4</v>
+      </c>
+      <c r="R647" t="n">
+        <v>16</v>
+      </c>
+      <c r="S647" t="n">
+        <v>34</v>
+      </c>
+      <c r="T647" t="b">
+        <v>1</v>
+      </c>
+      <c r="U647" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>PO-2026-00907</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>S101</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>PT Gunung Raja Paksi</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Local Steel</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Hot-rolled steel plate</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>tonne</t>
+        </is>
+      </c>
+      <c r="G648" t="n">
+        <v>170</v>
+      </c>
+      <c r="H648" t="n">
+        <v>800</v>
+      </c>
+      <c r="I648" t="n">
+        <v>136000</v>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="O648" t="n">
+        <v>6</v>
+      </c>
+      <c r="P648" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q648" t="n">
+        <v>7</v>
+      </c>
+      <c r="R648" t="n">
+        <v>21</v>
+      </c>
+      <c r="S648" t="n">
+        <v>56</v>
+      </c>
+      <c r="T648" t="b">
+        <v>0</v>
+      </c>
+      <c r="U648" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -58034,7 +58643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z56"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58158,16 +58767,6 @@
           <t>composite_score</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>calculated_tier</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>tier_mismatch</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -58254,14 +58853,6 @@
       <c r="X2" t="n">
         <v>90.17</v>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z2" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -58348,14 +58939,6 @@
       <c r="X3" t="n">
         <v>89.05</v>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z3" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -58442,14 +59025,6 @@
       <c r="X4" t="n">
         <v>86.51000000000001</v>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z4" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -58536,14 +59111,6 @@
       <c r="X5" t="n">
         <v>80.84999999999999</v>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -58630,14 +59197,6 @@
       <c r="X6" t="n">
         <v>74</v>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z6" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -58724,14 +59283,6 @@
       <c r="X7" t="n">
         <v>78.63</v>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -58818,14 +59369,6 @@
       <c r="X8" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z8" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -58912,14 +59455,6 @@
       <c r="X9" t="n">
         <v>76.61</v>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -59006,14 +59541,6 @@
       <c r="X10" t="n">
         <v>82.61</v>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -59100,14 +59627,6 @@
       <c r="X11" t="n">
         <v>79.69</v>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -59194,14 +59713,6 @@
       <c r="X12" t="n">
         <v>83.78</v>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z12" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -59288,14 +59799,6 @@
       <c r="X13" t="n">
         <v>67.79000000000001</v>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -59382,14 +59885,6 @@
       <c r="X14" t="n">
         <v>76.91</v>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z14" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -59476,14 +59971,6 @@
       <c r="X15" t="n">
         <v>81.05</v>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -59570,14 +60057,6 @@
       <c r="X16" t="n">
         <v>83.31999999999999</v>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -59664,14 +60143,6 @@
       <c r="X17" t="n">
         <v>72.29000000000001</v>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -59758,14 +60229,6 @@
       <c r="X18" t="n">
         <v>85.56999999999999</v>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -59852,14 +60315,6 @@
       <c r="X19" t="n">
         <v>72.81999999999999</v>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -59946,14 +60401,6 @@
       <c r="X20" t="n">
         <v>76.63</v>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z20" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -60040,14 +60487,6 @@
       <c r="X21" t="n">
         <v>73.28</v>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -60134,14 +60573,6 @@
       <c r="X22" t="n">
         <v>75.31999999999999</v>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z22" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -60228,14 +60659,6 @@
       <c r="X23" t="n">
         <v>66.88</v>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z23" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -60322,14 +60745,6 @@
       <c r="X24" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -60416,14 +60831,6 @@
       <c r="X25" t="n">
         <v>86.64</v>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -60510,14 +60917,6 @@
       <c r="X26" t="n">
         <v>82.87</v>
       </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -60604,14 +61003,6 @@
       <c r="X27" t="n">
         <v>83.38</v>
       </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z27" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -60698,14 +61089,6 @@
       <c r="X28" t="n">
         <v>77.84</v>
       </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z28" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -60792,14 +61175,6 @@
       <c r="X29" t="n">
         <v>72.97</v>
       </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -60886,14 +61261,6 @@
       <c r="X30" t="n">
         <v>71.86</v>
       </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z30" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -60980,14 +61347,6 @@
       <c r="X31" t="n">
         <v>80.03</v>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -61074,14 +61433,6 @@
       <c r="X32" t="n">
         <v>80.44</v>
       </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z32" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -61168,14 +61519,6 @@
       <c r="X33" t="n">
         <v>66.64</v>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z33" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -61262,14 +61605,6 @@
       <c r="X34" t="n">
         <v>63.3</v>
       </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z34" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -61356,14 +61691,6 @@
       <c r="X35" t="n">
         <v>68.23</v>
       </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z35" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -61450,14 +61777,6 @@
       <c r="X36" t="n">
         <v>68.13</v>
       </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z36" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -61544,14 +61863,6 @@
       <c r="X37" t="n">
         <v>74.83</v>
       </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z37" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -61638,14 +61949,6 @@
       <c r="X38" t="n">
         <v>52.66</v>
       </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="Z38" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -61732,14 +62035,6 @@
       <c r="X39" t="n">
         <v>78.45</v>
       </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z39" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -61826,14 +62121,6 @@
       <c r="X40" t="n">
         <v>69.63</v>
       </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z40" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -61920,14 +62207,6 @@
       <c r="X41" t="n">
         <v>73.34</v>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z41" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -62014,14 +62293,6 @@
       <c r="X42" t="n">
         <v>71.75</v>
       </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z42" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -62108,14 +62379,6 @@
       <c r="X43" t="n">
         <v>75.62</v>
       </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z43" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -62202,14 +62465,6 @@
       <c r="X44" t="n">
         <v>80.75</v>
       </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z44" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -62296,14 +62551,6 @@
       <c r="X45" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z45" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -62390,14 +62637,6 @@
       <c r="X46" t="n">
         <v>74.41</v>
       </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z46" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -62484,14 +62723,6 @@
       <c r="X47" t="n">
         <v>84.72</v>
       </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z47" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -62525,66 +62756,58 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>891500</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>127357.14</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>43.71</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P48" t="n">
-        <v>86.20999999999999</v>
+        <v>68</v>
       </c>
       <c r="Q48" t="n">
-        <v>10.58</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>77.5</v>
+        <v>71</v>
       </c>
       <c r="T48" t="n">
-        <v>50</v>
+        <v>73.81</v>
       </c>
       <c r="U48" t="n">
-        <v>55.32</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="W48" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="X48" t="n">
-        <v>53.82</v>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="Z48" t="b">
-        <v>0</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -62672,14 +62895,6 @@
       <c r="X49" t="n">
         <v>83.88</v>
       </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z49" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -62766,14 +62981,6 @@
       <c r="X50" t="n">
         <v>64.72</v>
       </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z50" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -62860,14 +63067,6 @@
       <c r="X51" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z51" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -62954,14 +63153,6 @@
       <c r="X52" t="n">
         <v>83.33</v>
       </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z52" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -63048,14 +63239,6 @@
       <c r="X53" t="n">
         <v>68.73999999999999</v>
       </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z53" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -63142,14 +63325,6 @@
       <c r="X54" t="n">
         <v>88.76000000000001</v>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="Z54" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -63236,14 +63411,6 @@
       <c r="X55" t="n">
         <v>64.34</v>
       </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z55" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -63329,14 +63496,6 @@
       </c>
       <c r="X56" t="n">
         <v>68.94</v>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="Z56" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
